--- a/results/2026-04-07-SAT-precedence-graph/results_maxsat_scl_cont_prec_graph_120s.xlsx
+++ b/results/2026-04-07-SAT-precedence-graph/results_maxsat_scl_cont_prec_graph_120s.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17715"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="34515"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 <file path=xl/connections.xml><?xml version="1.0" encoding="utf-8"?>
 <connections xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <connection id="1" name="results_maxsat_scl_cont_prec_graph_120s" type="6" refreshedVersion="5" background="1" saveData="1">
-    <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results\2026-04-07-SAT-precedence-graph\raw_data\csv\results_maxsat_scl_cont_prec_graph_120s.csv" comma="1">
+    <textPr codePage="437" sourceFile="D:\github\maxsattrainscheduling\results_maxsat_scl_cont_prec_graph_120s.csv" comma="1">
       <textFields count="26">
         <textField/>
         <textField/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="105">
   <si>
     <t>algorithm_time</t>
   </si>
@@ -162,9 +162,6 @@
     <t>origA3</t>
   </si>
   <si>
-    <t>no_solution</t>
-  </si>
-  <si>
     <t>origA4</t>
   </si>
   <si>
@@ -225,34 +222,34 @@
     <t>origB11</t>
   </si>
   <si>
+    <t>origB12</t>
+  </si>
+  <si>
+    <t>trackA1</t>
+  </si>
+  <si>
+    <t>trackA2</t>
+  </si>
+  <si>
+    <t>trackA3</t>
+  </si>
+  <si>
+    <t>trackA4</t>
+  </si>
+  <si>
+    <t>trackA5</t>
+  </si>
+  <si>
+    <t>trackA6</t>
+  </si>
+  <si>
+    <t>trackA7</t>
+  </si>
+  <si>
+    <t>trackA8</t>
+  </si>
+  <si>
     <t>timeout</t>
-  </si>
-  <si>
-    <t>origB12</t>
-  </si>
-  <si>
-    <t>trackA1</t>
-  </si>
-  <si>
-    <t>trackA2</t>
-  </si>
-  <si>
-    <t>trackA3</t>
-  </si>
-  <si>
-    <t>trackA4</t>
-  </si>
-  <si>
-    <t>trackA5</t>
-  </si>
-  <si>
-    <t>trackA6</t>
-  </si>
-  <si>
-    <t>trackA7</t>
-  </si>
-  <si>
-    <t>trackA8</t>
   </si>
   <si>
     <t>trackA9</t>
@@ -438,8 +435,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
@@ -738,7 +736,7 @@
     <col min="7" max="7" width="15.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="6" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
@@ -749,12 +747,12 @@
     <col min="18" max="18" width="12" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="19.7109375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="8.140625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="12" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="24.5703125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:30" x14ac:dyDescent="0.25">
@@ -836,22 +834,22 @@
       <c r="Z1" t="s">
         <v>25</v>
       </c>
-      <c r="AB1" s="1" t="s">
+      <c r="AB1" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="AC1" s="1" t="s">
+      <c r="AD1" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="AD1" s="1" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0.66181490499999995</v>
+        <v>0.64418350199999996</v>
       </c>
       <c r="B2">
-        <v>1.42558326629123</v>
+        <v>1.23250201126307</v>
       </c>
       <c r="C2">
         <v>20.931034088134702</v>
@@ -872,78 +870,78 @@
         <v>0</v>
       </c>
       <c r="I2">
-        <v>915</v>
+        <v>59</v>
       </c>
       <c r="J2">
-        <v>5755</v>
+        <v>8171</v>
       </c>
       <c r="K2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L2" t="s">
         <v>27</v>
       </c>
       <c r="M2">
-        <v>455</v>
+        <v>222</v>
       </c>
       <c r="N2">
-        <v>1772</v>
+        <v>1532</v>
       </c>
       <c r="O2">
-        <v>455</v>
+        <v>222</v>
       </c>
       <c r="P2">
-        <v>844</v>
+        <v>11</v>
       </c>
       <c r="Q2">
         <v>1</v>
       </c>
       <c r="R2">
-        <v>850.09583499999997</v>
+        <v>645.54982199999995</v>
       </c>
       <c r="S2" t="s">
         <v>28</v>
       </c>
       <c r="T2">
-        <v>0.187664572</v>
+        <v>6.3478999999999999E-4</v>
       </c>
       <c r="U2" t="s">
         <v>29</v>
       </c>
       <c r="V2">
-        <v>0.84947895399999995</v>
+        <v>0.64481774800000002</v>
       </c>
       <c r="W2">
         <v>29</v>
       </c>
       <c r="X2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="Y2">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="Z2">
-        <v>5755</v>
-      </c>
-      <c r="AB2" s="2">
+        <v>8171</v>
+      </c>
+      <c r="AB2" s="3">
         <f>AVERAGE(R2:R25)</f>
-        <v>41110.350082124998</v>
-      </c>
-      <c r="AC2" s="2">
+        <v>254.30308654166672</v>
+      </c>
+      <c r="AC2" s="3">
         <f>AVERAGE(R26:R49)</f>
-        <v>53576.184176541668</v>
-      </c>
-      <c r="AD2" s="2">
+        <v>15962.766270666629</v>
+      </c>
+      <c r="AD2" s="3">
         <f>AVERAGE(R50:R73)</f>
-        <v>60763.30597554164</v>
+        <v>17567.896641874995</v>
       </c>
     </row>
     <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>5.2831277999999898E-2</v>
+        <v>3.1362356000000001E-2</v>
       </c>
       <c r="B3">
-        <v>1.58153846153846</v>
+        <v>2.06153846153846</v>
       </c>
       <c r="C3">
         <v>19</v>
@@ -955,7 +953,7 @@
         <v>33</v>
       </c>
       <c r="F3">
-        <v>5804</v>
+        <v>6900</v>
       </c>
       <c r="G3" t="s">
         <v>26</v>
@@ -964,61 +962,67 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1357</v>
+        <v>131</v>
       </c>
       <c r="J3">
-        <v>5804</v>
+        <v>8159</v>
       </c>
       <c r="K3">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L3" t="s">
         <v>30</v>
       </c>
       <c r="M3">
-        <v>452</v>
+        <v>795</v>
       </c>
       <c r="N3">
-        <v>1542</v>
+        <v>2010</v>
       </c>
       <c r="O3">
-        <v>452</v>
+        <v>795</v>
       </c>
       <c r="P3">
-        <v>1318</v>
+        <v>28</v>
       </c>
       <c r="Q3">
         <v>1</v>
       </c>
       <c r="R3">
-        <v>451.46519599999999</v>
+        <v>48.119114000000003</v>
       </c>
       <c r="S3" t="s">
         <v>28</v>
       </c>
       <c r="T3">
-        <v>0.397831781</v>
+        <v>1.6495770999999999E-2</v>
       </c>
       <c r="U3" t="s">
         <v>29</v>
       </c>
       <c r="V3">
-        <v>0.45066236599999998</v>
+        <v>4.7857602999999999E-2</v>
       </c>
       <c r="W3">
         <v>25</v>
       </c>
       <c r="X3">
-        <v>23</v>
+        <v>60</v>
       </c>
       <c r="Y3">
-        <v>16</v>
+        <v>41</v>
       </c>
       <c r="Z3">
-        <v>5804</v>
+        <v>8159</v>
       </c>
     </row>
     <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>2.0906695999999999E-2</v>
+      </c>
+      <c r="B4">
+        <v>1.6857923497267699</v>
+      </c>
       <c r="C4">
         <v>22.375</v>
       </c>
@@ -1028,34 +1032,76 @@
       <c r="E4">
         <v>33</v>
       </c>
+      <c r="F4">
+        <v>3144</v>
+      </c>
       <c r="G4" t="s">
         <v>26</v>
       </c>
       <c r="H4">
         <v>2</v>
       </c>
+      <c r="I4">
+        <v>164</v>
+      </c>
+      <c r="J4">
+        <v>4055</v>
+      </c>
+      <c r="K4">
+        <v>8</v>
+      </c>
       <c r="L4" t="s">
         <v>31</v>
       </c>
+      <c r="M4">
+        <v>432</v>
+      </c>
+      <c r="N4">
+        <v>1234</v>
+      </c>
+      <c r="O4">
+        <v>432</v>
+      </c>
+      <c r="P4">
+        <v>77</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
       <c r="R4">
-        <v>120000</v>
+        <v>36.610951999999997</v>
       </c>
       <c r="S4" t="s">
         <v>28</v>
       </c>
+      <c r="T4">
+        <v>1.5570321E-2</v>
+      </c>
       <c r="U4" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V4">
+        <v>3.6476428999999998E-2</v>
       </c>
       <c r="W4">
         <v>16</v>
       </c>
+      <c r="X4">
+        <v>17</v>
+      </c>
+      <c r="Y4">
+        <v>68</v>
+      </c>
+      <c r="Z4">
+        <v>4055</v>
+      </c>
     </row>
     <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>2.5780005000000002E-2</v>
+        <v>1.5829227000000001E-2</v>
       </c>
       <c r="B5">
-        <v>1.63224637681159</v>
+        <v>1.8025362318840501</v>
       </c>
       <c r="C5">
         <v>19.214284896850501</v>
@@ -1067,7 +1113,7 @@
         <v>33</v>
       </c>
       <c r="F5">
-        <v>2706</v>
+        <v>3511</v>
       </c>
       <c r="G5" t="s">
         <v>26</v>
@@ -1076,66 +1122,66 @@
         <v>3</v>
       </c>
       <c r="I5">
-        <v>504</v>
+        <v>89</v>
       </c>
       <c r="J5">
-        <v>2706</v>
+        <v>4041</v>
       </c>
       <c r="K5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M5">
-        <v>303</v>
+        <v>389</v>
       </c>
       <c r="N5">
-        <v>901</v>
+        <v>995</v>
       </c>
       <c r="O5">
-        <v>303</v>
+        <v>389</v>
       </c>
       <c r="P5">
-        <v>461</v>
+        <v>12</v>
       </c>
       <c r="Q5">
         <v>1</v>
       </c>
       <c r="R5">
-        <v>87.261798999999996</v>
+        <v>18.668941</v>
       </c>
       <c r="S5" t="s">
         <v>28</v>
       </c>
       <c r="T5">
-        <v>6.1206550999999998E-2</v>
+        <v>2.7494279999999999E-3</v>
       </c>
       <c r="U5" t="s">
         <v>29</v>
       </c>
       <c r="V5">
-        <v>8.6985977000000006E-2</v>
+        <v>1.8578179E-2</v>
       </c>
       <c r="W5">
         <v>14</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="Z5">
-        <v>2706</v>
+        <v>4041</v>
       </c>
     </row>
     <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>2.4674349999999901E-2</v>
+        <v>1.3935661E-2</v>
       </c>
       <c r="B6">
-        <v>1.60759493670886</v>
+        <v>1.3818565400843801</v>
       </c>
       <c r="C6">
         <v>19.25</v>
@@ -1147,7 +1193,7 @@
         <v>33</v>
       </c>
       <c r="F6">
-        <v>2634</v>
+        <v>3246</v>
       </c>
       <c r="G6" t="s">
         <v>26</v>
@@ -1156,66 +1202,66 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>504</v>
+        <v>53</v>
       </c>
       <c r="J6">
-        <v>2634</v>
+        <v>4086</v>
       </c>
       <c r="K6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="M6">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="N6">
-        <v>762</v>
+        <v>655</v>
       </c>
       <c r="O6">
-        <v>243</v>
+        <v>139</v>
       </c>
       <c r="P6">
-        <v>448</v>
+        <v>13</v>
       </c>
       <c r="Q6">
         <v>1</v>
       </c>
       <c r="R6">
-        <v>76.687393999999998</v>
+        <v>14.760818</v>
       </c>
       <c r="S6" t="s">
         <v>28</v>
       </c>
       <c r="T6">
-        <v>5.1755997999999998E-2</v>
+        <v>7.7177300000000001E-4</v>
       </c>
       <c r="U6" t="s">
         <v>29</v>
       </c>
       <c r="V6">
-        <v>7.6429859000000003E-2</v>
+        <v>1.4706695000000001E-2</v>
       </c>
       <c r="W6">
         <v>12</v>
       </c>
       <c r="X6">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Z6">
-        <v>2634</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1.6307456000000001E-2</v>
+        <v>1.3736302000000001E-2</v>
       </c>
       <c r="B7">
-        <v>1.6633986928104501</v>
+        <v>1.63398692810457</v>
       </c>
       <c r="C7">
         <v>18.625</v>
@@ -1227,7 +1273,7 @@
         <v>33</v>
       </c>
       <c r="F7">
-        <v>2068</v>
+        <v>2113</v>
       </c>
       <c r="G7" t="s">
         <v>26</v>
@@ -1236,46 +1282,46 @@
         <v>5</v>
       </c>
       <c r="I7">
-        <v>254</v>
+        <v>88</v>
       </c>
       <c r="J7">
-        <v>2068</v>
+        <v>4079</v>
       </c>
       <c r="K7">
         <v>4</v>
       </c>
       <c r="L7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M7">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="N7">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="O7">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="P7">
-        <v>195</v>
+        <v>20</v>
       </c>
       <c r="Q7">
         <v>1</v>
       </c>
       <c r="R7">
-        <v>24.847843999999998</v>
+        <v>15.286346999999999</v>
       </c>
       <c r="S7" t="s">
         <v>28</v>
       </c>
       <c r="T7">
-        <v>8.4116030000000001E-3</v>
+        <v>1.503206E-3</v>
       </c>
       <c r="U7" t="s">
         <v>29</v>
       </c>
       <c r="V7">
-        <v>2.4718441000000001E-2</v>
+        <v>1.5239000000000001E-2</v>
       </c>
       <c r="W7">
         <v>8</v>
@@ -1284,18 +1330,18 @@
         <v>5</v>
       </c>
       <c r="Y7">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="Z7">
-        <v>2068</v>
+        <v>4079</v>
       </c>
     </row>
     <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8">
-        <v>1.8457914999999998E-2</v>
+        <v>1.6277130000000001E-2</v>
       </c>
       <c r="B8">
-        <v>2.88095238095238</v>
+        <v>2.6047619047618999</v>
       </c>
       <c r="C8">
         <v>12.625</v>
@@ -1316,46 +1362,46 @@
         <v>6</v>
       </c>
       <c r="I8">
-        <v>310</v>
+        <v>182</v>
       </c>
       <c r="J8">
         <v>1918</v>
       </c>
       <c r="K8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M8">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="N8">
-        <v>605</v>
+        <v>547</v>
       </c>
       <c r="O8">
-        <v>347</v>
+        <v>295</v>
       </c>
       <c r="P8">
-        <v>248</v>
+        <v>116</v>
       </c>
       <c r="Q8">
         <v>1</v>
       </c>
       <c r="R8">
-        <v>47.279204</v>
+        <v>29.391349000000002</v>
       </c>
       <c r="S8" t="s">
         <v>28</v>
       </c>
       <c r="T8">
-        <v>2.8688453999999999E-2</v>
+        <v>1.2972190999999999E-2</v>
       </c>
       <c r="U8" t="s">
         <v>29</v>
       </c>
       <c r="V8">
-        <v>4.7145839000000002E-2</v>
+        <v>2.9248799999999998E-2</v>
       </c>
       <c r="W8">
         <v>8</v>
@@ -1364,7 +1410,7 @@
         <v>8</v>
       </c>
       <c r="Y8">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="Z8">
         <v>1918</v>
@@ -1372,10 +1418,10 @@
     </row>
     <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9">
-        <v>0.234800861</v>
+        <v>7.8049672E-2</v>
       </c>
       <c r="B9">
-        <v>2.8913043478260798</v>
+        <v>4.7771739130434696</v>
       </c>
       <c r="C9">
         <v>19.214284896850501</v>
@@ -1387,7 +1433,7 @@
         <v>33</v>
       </c>
       <c r="F9">
-        <v>23143</v>
+        <v>31118</v>
       </c>
       <c r="G9" t="s">
         <v>26</v>
@@ -1396,61 +1442,67 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>3678</v>
+        <v>328</v>
       </c>
       <c r="J9">
-        <v>23143</v>
+        <v>32727</v>
       </c>
       <c r="K9">
+        <v>59</v>
+      </c>
+      <c r="L9" t="s">
+        <v>36</v>
+      </c>
+      <c r="M9">
+        <v>3120</v>
+      </c>
+      <c r="N9">
+        <v>5274</v>
+      </c>
+      <c r="O9">
+        <v>3120</v>
+      </c>
+      <c r="P9">
         <v>22</v>
       </c>
-      <c r="L9" t="s">
-        <v>37</v>
-      </c>
-      <c r="M9">
-        <v>1486</v>
-      </c>
-      <c r="N9">
-        <v>3192</v>
-      </c>
-      <c r="O9">
-        <v>1486</v>
-      </c>
-      <c r="P9">
-        <v>3632</v>
-      </c>
       <c r="Q9">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="R9">
-        <v>11649.588787000001</v>
+        <v>211.60058699999999</v>
       </c>
       <c r="S9" t="s">
         <v>28</v>
       </c>
       <c r="T9">
-        <v>11.409546548</v>
+        <v>0.13307174899999999</v>
       </c>
       <c r="U9" t="s">
         <v>29</v>
       </c>
       <c r="V9">
-        <v>11.644346565999999</v>
+        <v>0.211120748</v>
       </c>
       <c r="W9">
         <v>28</v>
       </c>
       <c r="X9">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="Y9">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="Z9">
-        <v>23143</v>
+        <v>32727</v>
       </c>
     </row>
     <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>3.2338659999999998E-2</v>
+      </c>
+      <c r="B10">
+        <v>2.2177615571776101</v>
+      </c>
       <c r="C10">
         <v>20.049999237060501</v>
       </c>
@@ -1460,34 +1512,76 @@
       <c r="E10">
         <v>33</v>
       </c>
+      <c r="F10">
+        <v>7929</v>
+      </c>
       <c r="G10" t="s">
         <v>26</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
+      <c r="I10">
+        <v>144</v>
+      </c>
+      <c r="J10">
+        <v>8039</v>
+      </c>
+      <c r="K10">
+        <v>11</v>
+      </c>
       <c r="L10" t="s">
-        <v>38</v>
+        <v>37</v>
+      </c>
+      <c r="M10">
+        <v>844</v>
+      </c>
+      <c r="N10">
+        <v>1823</v>
+      </c>
+      <c r="O10">
+        <v>844</v>
+      </c>
+      <c r="P10">
+        <v>13</v>
+      </c>
+      <c r="Q10">
+        <v>4</v>
       </c>
       <c r="R10">
-        <v>120000</v>
+        <v>51.460239999999999</v>
       </c>
       <c r="S10" t="s">
         <v>28</v>
       </c>
+      <c r="T10">
+        <v>1.8923104999999999E-2</v>
+      </c>
       <c r="U10" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V10">
+        <v>5.1261149999999998E-2</v>
       </c>
       <c r="W10">
         <v>20</v>
       </c>
+      <c r="X10">
+        <v>48</v>
+      </c>
+      <c r="Y10">
+        <v>78</v>
+      </c>
+      <c r="Z10">
+        <v>8039</v>
+      </c>
     </row>
     <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11">
-        <v>5.3662387000000103E-2</v>
+        <v>2.2202746999999998E-2</v>
       </c>
       <c r="B11">
-        <v>1.9307086614173199</v>
+        <v>3.0425196850393701</v>
       </c>
       <c r="C11">
         <v>18.176469802856399</v>
@@ -1499,7 +1593,7 @@
         <v>33</v>
       </c>
       <c r="F11">
-        <v>4746</v>
+        <v>6688</v>
       </c>
       <c r="G11" t="s">
         <v>26</v>
@@ -1508,66 +1602,66 @@
         <v>9</v>
       </c>
       <c r="I11">
-        <v>981</v>
+        <v>145</v>
       </c>
       <c r="J11">
-        <v>4746</v>
+        <v>8185</v>
       </c>
       <c r="K11">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="L11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M11">
-        <v>509</v>
+        <v>1041</v>
       </c>
       <c r="N11">
-        <v>1226</v>
+        <v>1932</v>
       </c>
       <c r="O11">
-        <v>509</v>
+        <v>1041</v>
       </c>
       <c r="P11">
-        <v>929</v>
+        <v>16</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R11">
-        <v>1886.320903</v>
+        <v>35.972084000000002</v>
       </c>
       <c r="S11" t="s">
         <v>28</v>
       </c>
       <c r="T11">
-        <v>1.8315403219999999</v>
+        <v>1.3603814000000001E-2</v>
       </c>
       <c r="U11" t="s">
         <v>29</v>
       </c>
       <c r="V11">
-        <v>1.885201777</v>
+        <v>3.5806027999999997E-2</v>
       </c>
       <c r="W11">
         <v>17</v>
       </c>
       <c r="X11">
-        <v>21</v>
+        <v>66</v>
       </c>
       <c r="Y11">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="Z11">
-        <v>4746</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12">
-        <v>0.180722090999999</v>
+        <v>4.1078364999999999E-2</v>
       </c>
       <c r="B12">
-        <v>1.9090163934426201</v>
+        <v>1.8713114754098299</v>
       </c>
       <c r="C12">
         <v>19.8333339691162</v>
@@ -1579,7 +1673,7 @@
         <v>33</v>
       </c>
       <c r="F12">
-        <v>3827</v>
+        <v>3962</v>
       </c>
       <c r="G12" t="s">
         <v>26</v>
@@ -1588,66 +1682,66 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>2694</v>
+        <v>86</v>
       </c>
       <c r="J12">
-        <v>3827</v>
+        <v>4038</v>
       </c>
       <c r="K12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="L12" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="M12">
-        <v>921</v>
+        <v>872</v>
       </c>
       <c r="N12">
-        <v>2329</v>
+        <v>2283</v>
       </c>
       <c r="O12">
-        <v>921</v>
+        <v>872</v>
       </c>
       <c r="P12">
-        <v>2608</v>
+        <v>22</v>
       </c>
       <c r="Q12">
         <v>1</v>
       </c>
       <c r="R12">
-        <v>4362.6280809999998</v>
+        <v>50.279814999999999</v>
       </c>
       <c r="S12" t="s">
         <v>28</v>
       </c>
       <c r="T12">
-        <v>4.1784558010000001</v>
+        <v>9.0163670000000008E-3</v>
       </c>
       <c r="U12" t="s">
         <v>29</v>
       </c>
       <c r="V12">
-        <v>4.3591772799999999</v>
+        <v>5.0094118E-2</v>
       </c>
       <c r="W12">
         <v>30</v>
       </c>
       <c r="X12">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="Y12">
-        <v>39</v>
+        <v>23</v>
       </c>
       <c r="Z12">
-        <v>3827</v>
+        <v>4038</v>
       </c>
     </row>
     <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13">
-        <v>0.189900441</v>
+        <v>4.7554486999999999E-2</v>
       </c>
       <c r="B13">
-        <v>2.0401929260450098</v>
+        <v>2.2033762057877802</v>
       </c>
       <c r="C13">
         <v>21.714284896850501</v>
@@ -1659,7 +1753,7 @@
         <v>33</v>
       </c>
       <c r="F13">
-        <v>4950</v>
+        <v>5111</v>
       </c>
       <c r="G13" t="s">
         <v>26</v>
@@ -1668,61 +1762,67 @@
         <v>11</v>
       </c>
       <c r="I13">
-        <v>3009</v>
+        <v>278</v>
       </c>
       <c r="J13">
-        <v>4950</v>
+        <v>8104</v>
       </c>
       <c r="K13">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="M13">
-        <v>1075</v>
+        <v>1218</v>
       </c>
       <c r="N13">
-        <v>2538</v>
+        <v>2741</v>
       </c>
       <c r="O13">
-        <v>1075</v>
+        <v>1218</v>
       </c>
       <c r="P13">
-        <v>2943</v>
+        <v>201</v>
       </c>
       <c r="Q13">
         <v>1</v>
       </c>
       <c r="R13">
-        <v>6903.2734979999996</v>
+        <v>165.98095000000001</v>
       </c>
       <c r="S13" t="s">
         <v>28</v>
       </c>
       <c r="T13">
-        <v>6.7106672849999898</v>
+        <v>0.118109824</v>
       </c>
       <c r="U13" t="s">
         <v>29</v>
       </c>
       <c r="V13">
-        <v>6.9005670800000001</v>
+        <v>0.16566372800000001</v>
       </c>
       <c r="W13">
         <v>28</v>
       </c>
       <c r="X13">
-        <v>42</v>
+        <v>54</v>
       </c>
       <c r="Y13">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Z13">
-        <v>4950</v>
+        <v>8104</v>
       </c>
     </row>
     <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>1.2860528E-2</v>
+      </c>
+      <c r="B14">
+        <v>1.1433021806853501</v>
+      </c>
       <c r="C14">
         <v>17.3333339691162</v>
       </c>
@@ -1732,31 +1832,73 @@
       <c r="E14">
         <v>25</v>
       </c>
+      <c r="F14">
+        <v>1377</v>
+      </c>
       <c r="G14" t="s">
         <v>26</v>
       </c>
       <c r="H14">
         <v>12</v>
       </c>
+      <c r="I14">
+        <v>49</v>
+      </c>
+      <c r="J14">
+        <v>1532</v>
+      </c>
+      <c r="K14">
+        <v>4</v>
+      </c>
       <c r="L14" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+      <c r="M14">
+        <v>80</v>
+      </c>
+      <c r="N14">
+        <v>734</v>
+      </c>
+      <c r="O14">
+        <v>80</v>
+      </c>
+      <c r="P14">
+        <v>9</v>
+      </c>
+      <c r="Q14">
+        <v>1</v>
       </c>
       <c r="R14">
-        <v>120000</v>
+        <v>13.138209</v>
       </c>
       <c r="S14" t="s">
         <v>28</v>
       </c>
+      <c r="T14">
+        <v>2.2045499999999999E-4</v>
+      </c>
       <c r="U14" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V14">
+        <v>1.3080395999999999E-2</v>
       </c>
       <c r="W14">
         <v>18</v>
       </c>
+      <c r="X14">
+        <v>2</v>
+      </c>
+      <c r="Y14">
+        <v>36</v>
+      </c>
+      <c r="Z14">
+        <v>1532</v>
+      </c>
     </row>
     <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15">
-        <v>1.20231119999999E-2</v>
+        <v>1.2658007999999899E-2</v>
       </c>
       <c r="B15">
         <v>1.41830065359477</v>
@@ -1789,7 +1931,7 @@
         <v>3</v>
       </c>
       <c r="L15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="M15">
         <v>58</v>
@@ -1807,19 +1949,19 @@
         <v>1</v>
       </c>
       <c r="R15">
-        <v>12.227251000000001</v>
+        <v>12.90615</v>
       </c>
       <c r="S15" t="s">
         <v>28</v>
       </c>
       <c r="T15">
-        <v>1.87288E-4</v>
+        <v>2.29216E-4</v>
       </c>
       <c r="U15" t="s">
         <v>29</v>
       </c>
       <c r="V15">
-        <v>1.2209863E-2</v>
+        <v>1.2886671000000001E-2</v>
       </c>
       <c r="W15">
         <v>5</v>
@@ -1835,6 +1977,12 @@
       </c>
     </row>
     <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1.2521614E-2</v>
+      </c>
+      <c r="B16">
+        <v>1.9075144508670501</v>
+      </c>
       <c r="C16">
         <v>16.799999237060501</v>
       </c>
@@ -1844,34 +1992,76 @@
       <c r="E16">
         <v>20</v>
       </c>
+      <c r="F16">
+        <v>974</v>
+      </c>
       <c r="G16" t="s">
         <v>26</v>
       </c>
       <c r="H16">
         <v>14</v>
       </c>
+      <c r="I16">
+        <v>47</v>
+      </c>
+      <c r="J16">
+        <v>1014</v>
+      </c>
+      <c r="K16">
+        <v>6</v>
+      </c>
       <c r="L16" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="M16">
+        <v>131</v>
+      </c>
+      <c r="N16">
+        <v>330</v>
+      </c>
+      <c r="O16">
+        <v>131</v>
+      </c>
+      <c r="P16">
+        <v>8</v>
+      </c>
+      <c r="Q16">
+        <v>1</v>
       </c>
       <c r="R16">
-        <v>120000</v>
+        <v>12.849919999999999</v>
       </c>
       <c r="S16" t="s">
         <v>28</v>
       </c>
+      <c r="T16">
+        <v>3.0416200000000002E-4</v>
+      </c>
       <c r="U16" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V16">
+        <v>1.2825260999999999E-2</v>
       </c>
       <c r="W16">
         <v>5</v>
       </c>
+      <c r="X16">
+        <v>3</v>
+      </c>
+      <c r="Y16">
+        <v>34</v>
+      </c>
+      <c r="Z16">
+        <v>1014</v>
+      </c>
     </row>
     <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17">
-        <v>2.38835419999999E-2</v>
+        <v>3.3309635999999997E-2</v>
       </c>
       <c r="B17">
-        <v>2.4635258358662599</v>
+        <v>2.5744680851063801</v>
       </c>
       <c r="C17">
         <v>15.949999809265099</v>
@@ -1892,61 +2082,67 @@
         <v>15</v>
       </c>
       <c r="I17">
-        <v>423</v>
+        <v>461</v>
       </c>
       <c r="J17">
         <v>53607</v>
       </c>
       <c r="K17">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M17">
-        <v>653</v>
+        <v>797</v>
       </c>
       <c r="N17">
-        <v>1621</v>
+        <v>1694</v>
       </c>
       <c r="O17">
-        <v>653</v>
+        <v>797</v>
       </c>
       <c r="P17">
-        <v>342</v>
+        <v>377</v>
       </c>
       <c r="Q17">
         <v>1</v>
       </c>
       <c r="R17">
-        <v>114.836687</v>
+        <v>267.91934700000002</v>
       </c>
       <c r="S17" t="s">
         <v>28</v>
       </c>
       <c r="T17">
-        <v>9.0687824E-2</v>
+        <v>0.23305114599999999</v>
       </c>
       <c r="U17" t="s">
         <v>29</v>
       </c>
       <c r="V17">
-        <v>0.11457069</v>
+        <v>0.266360072</v>
       </c>
       <c r="W17">
         <v>20</v>
       </c>
       <c r="X17">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="Y17">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Z17">
         <v>53607</v>
       </c>
     </row>
     <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>1.2409051000000001E-2</v>
+      </c>
+      <c r="B18">
+        <v>1.2896174863387899</v>
+      </c>
       <c r="C18">
         <v>17.799999237060501</v>
       </c>
@@ -1956,34 +2152,76 @@
       <c r="E18">
         <v>25</v>
       </c>
+      <c r="F18">
+        <v>312</v>
+      </c>
       <c r="G18" t="s">
         <v>26</v>
       </c>
       <c r="H18">
         <v>16</v>
       </c>
+      <c r="I18">
+        <v>51</v>
+      </c>
+      <c r="J18">
+        <v>412</v>
+      </c>
+      <c r="K18">
+        <v>3</v>
+      </c>
       <c r="L18" t="s">
-        <v>46</v>
+        <v>45</v>
+      </c>
+      <c r="M18">
+        <v>47</v>
+      </c>
+      <c r="N18">
+        <v>236</v>
+      </c>
+      <c r="O18">
+        <v>47</v>
+      </c>
+      <c r="P18">
+        <v>11</v>
+      </c>
+      <c r="Q18">
+        <v>1</v>
       </c>
       <c r="R18">
-        <v>120000</v>
+        <v>12.612686999999999</v>
       </c>
       <c r="S18" t="s">
         <v>28</v>
       </c>
+      <c r="T18">
+        <v>1.5097400000000001E-4</v>
+      </c>
       <c r="U18" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V18">
+        <v>1.2559486E-2</v>
       </c>
       <c r="W18">
         <v>5</v>
       </c>
+      <c r="X18">
+        <v>1</v>
+      </c>
+      <c r="Y18">
+        <v>37</v>
+      </c>
+      <c r="Z18">
+        <v>412</v>
+      </c>
     </row>
     <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19">
-        <v>1.1822902999999999E-2</v>
+        <v>1.1822219E-2</v>
       </c>
       <c r="B19">
-        <v>1.31847133757961</v>
+        <v>1.0254777070063601</v>
       </c>
       <c r="C19">
         <v>15.199999809265099</v>
@@ -2004,61 +2242,67 @@
         <v>17</v>
       </c>
       <c r="I19">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="J19">
         <v>176</v>
       </c>
       <c r="K19">
+        <v>2</v>
+      </c>
+      <c r="L19" t="s">
+        <v>46</v>
+      </c>
+      <c r="M19">
+        <v>0</v>
+      </c>
+      <c r="N19">
+        <v>161</v>
+      </c>
+      <c r="O19">
+        <v>0</v>
+      </c>
+      <c r="P19">
         <v>3</v>
-      </c>
-      <c r="L19" t="s">
-        <v>47</v>
-      </c>
-      <c r="M19">
-        <v>44</v>
-      </c>
-      <c r="N19">
-        <v>207</v>
-      </c>
-      <c r="O19">
-        <v>44</v>
-      </c>
-      <c r="P19">
-        <v>9</v>
       </c>
       <c r="Q19">
         <v>1</v>
       </c>
       <c r="R19">
-        <v>11.994260000000001</v>
+        <v>11.851194</v>
       </c>
       <c r="S19" t="s">
         <v>28</v>
       </c>
-      <c r="T19">
-        <v>1.5496299999999999E-4</v>
+      <c r="T19" s="1">
+        <v>1.0533999999999999E-5</v>
       </c>
       <c r="U19" t="s">
         <v>29</v>
       </c>
       <c r="V19">
-        <v>1.1977299E-2</v>
+        <v>1.183212E-2</v>
       </c>
       <c r="W19">
         <v>5</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y19">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="Z19">
         <v>176</v>
       </c>
     </row>
     <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>0.19613792699999899</v>
+      </c>
+      <c r="B20">
+        <v>8.1230158730158699</v>
+      </c>
       <c r="C20">
         <v>15.25</v>
       </c>
@@ -2068,31 +2312,73 @@
       <c r="E20">
         <v>25</v>
       </c>
+      <c r="F20">
+        <v>69450</v>
+      </c>
       <c r="G20" t="s">
         <v>26</v>
       </c>
       <c r="H20">
         <v>18</v>
       </c>
+      <c r="I20">
+        <v>2015</v>
+      </c>
+      <c r="J20">
+        <v>130171</v>
+      </c>
+      <c r="K20">
+        <v>153</v>
+      </c>
       <c r="L20" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="M20">
+        <v>7367</v>
+      </c>
+      <c r="N20">
+        <v>6141</v>
+      </c>
+      <c r="O20">
+        <v>7367</v>
+      </c>
+      <c r="P20">
+        <v>1726</v>
+      </c>
+      <c r="Q20">
+        <v>27</v>
       </c>
       <c r="R20">
-        <v>120000</v>
+        <v>4290.1427270000004</v>
       </c>
       <c r="S20" t="s">
         <v>28</v>
       </c>
+      <c r="T20">
+        <v>4.0890365290000004</v>
+      </c>
       <c r="U20" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V20">
+        <v>4.285173812</v>
       </c>
       <c r="W20">
         <v>24</v>
       </c>
+      <c r="X20">
+        <v>261</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>130171</v>
+      </c>
     </row>
     <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21">
-        <v>1.2014868E-2</v>
+        <v>1.2649295E-2</v>
       </c>
       <c r="B21">
         <v>1.2877697841726601</v>
@@ -2116,7 +2402,7 @@
         <v>19</v>
       </c>
       <c r="I21">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J21">
         <v>676</v>
@@ -2125,7 +2411,7 @@
         <v>2</v>
       </c>
       <c r="L21" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M21">
         <v>36</v>
@@ -2137,25 +2423,25 @@
         <v>36</v>
       </c>
       <c r="P21">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Q21">
         <v>1</v>
       </c>
       <c r="R21">
-        <v>12.330009</v>
+        <v>13.021036</v>
       </c>
       <c r="S21" t="s">
         <v>28</v>
       </c>
       <c r="T21">
-        <v>2.9654600000000002E-4</v>
+        <v>3.3953500000000002E-4</v>
       </c>
       <c r="U21" t="s">
         <v>29</v>
       </c>
       <c r="V21">
-        <v>1.2310913E-2</v>
+        <v>1.2988224E-2</v>
       </c>
       <c r="W21">
         <v>5</v>
@@ -2172,10 +2458,10 @@
     </row>
     <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>2.6351988999999999E-2</v>
+        <v>1.9788614E-2</v>
       </c>
       <c r="B22">
-        <v>2.7106598984771502</v>
+        <v>3.46192893401015</v>
       </c>
       <c r="C22">
         <v>13.571428298950099</v>
@@ -2196,61 +2482,67 @@
         <v>20</v>
       </c>
       <c r="I22">
-        <v>589</v>
+        <v>257</v>
       </c>
       <c r="J22">
         <v>5969</v>
       </c>
       <c r="K22">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M22">
-        <v>286</v>
+        <v>391</v>
       </c>
       <c r="N22">
-        <v>534</v>
+        <v>682</v>
       </c>
       <c r="O22">
-        <v>286</v>
+        <v>391</v>
       </c>
       <c r="P22">
-        <v>532</v>
+        <v>203</v>
       </c>
       <c r="Q22">
         <v>1</v>
       </c>
       <c r="R22">
-        <v>114.918181</v>
+        <v>40.313521000000001</v>
       </c>
       <c r="S22" t="s">
         <v>28</v>
       </c>
       <c r="T22">
-        <v>8.8313743E-2</v>
+        <v>2.0288365999999999E-2</v>
       </c>
       <c r="U22" t="s">
         <v>29</v>
       </c>
       <c r="V22">
-        <v>0.11466483600000001</v>
+        <v>4.0076399999999998E-2</v>
       </c>
       <c r="W22">
         <v>7</v>
       </c>
       <c r="X22">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="Y22">
-        <v>45</v>
+        <v>27</v>
       </c>
       <c r="Z22">
         <v>5969</v>
       </c>
     </row>
     <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A23">
+        <v>1.9813657999999901E-2</v>
+      </c>
+      <c r="B23">
+        <v>3.27368421052631</v>
+      </c>
       <c r="C23">
         <v>11.375</v>
       </c>
@@ -2260,34 +2552,76 @@
       <c r="E23">
         <v>25</v>
       </c>
+      <c r="F23">
+        <v>5747</v>
+      </c>
       <c r="G23" t="s">
         <v>26</v>
       </c>
       <c r="H23">
         <v>21</v>
       </c>
+      <c r="I23">
+        <v>237</v>
+      </c>
+      <c r="J23">
+        <v>5992</v>
+      </c>
+      <c r="K23">
+        <v>9</v>
+      </c>
       <c r="L23" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="M23">
+        <v>357</v>
+      </c>
+      <c r="N23">
+        <v>622</v>
+      </c>
+      <c r="O23">
+        <v>357</v>
+      </c>
+      <c r="P23">
+        <v>161</v>
+      </c>
+      <c r="Q23">
+        <v>1</v>
       </c>
       <c r="R23">
-        <v>120000</v>
+        <v>62.887148000000003</v>
       </c>
       <c r="S23" t="s">
         <v>28</v>
       </c>
+      <c r="T23">
+        <v>4.2878002999999998E-2</v>
+      </c>
       <c r="U23" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V23">
+        <v>6.2691021999999999E-2</v>
       </c>
       <c r="W23">
         <v>8</v>
       </c>
+      <c r="X23">
+        <v>14</v>
+      </c>
+      <c r="Y23">
+        <v>60</v>
+      </c>
+      <c r="Z23">
+        <v>5992</v>
+      </c>
     </row>
     <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24">
-        <v>0.235046538000005</v>
+        <v>1.8326737999999999E-2</v>
       </c>
       <c r="B24">
-        <v>2.7962264150943299</v>
+        <v>2.0742138364779801</v>
       </c>
       <c r="C24">
         <v>15.399999618530201</v>
@@ -2298,6 +2632,9 @@
       <c r="E24">
         <v>25</v>
       </c>
+      <c r="F24">
+        <v>78777</v>
+      </c>
       <c r="G24" t="s">
         <v>26</v>
       </c>
@@ -2305,66 +2642,66 @@
         <v>22</v>
       </c>
       <c r="I24">
-        <v>2576</v>
+        <v>88</v>
       </c>
       <c r="J24">
-        <v>75629</v>
+        <v>125404</v>
       </c>
       <c r="K24">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="L24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="M24">
-        <v>888</v>
+        <v>533</v>
       </c>
       <c r="N24">
-        <v>2223</v>
+        <v>1649</v>
       </c>
       <c r="O24">
-        <v>888</v>
+        <v>533</v>
       </c>
       <c r="P24">
-        <v>2513</v>
+        <v>13</v>
       </c>
       <c r="Q24">
         <v>1</v>
       </c>
       <c r="R24">
-        <v>120028.962069</v>
+        <v>28.389749999999999</v>
       </c>
       <c r="S24" t="s">
         <v>28</v>
       </c>
       <c r="T24">
-        <v>119.79391637099999</v>
+        <v>9.8520459999999997E-3</v>
       </c>
       <c r="U24" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="V24">
-        <v>120.028962069</v>
+        <v>2.8178041000000001E-2</v>
       </c>
       <c r="W24">
         <v>25</v>
       </c>
       <c r="X24">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="Y24">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="Z24">
-        <v>75700</v>
+        <v>125404</v>
       </c>
     </row>
     <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25">
-        <v>1.3041839E-2</v>
+        <v>1.3318699E-2</v>
       </c>
       <c r="B25">
-        <v>1.36752136752136</v>
+        <v>1.16239316239316</v>
       </c>
       <c r="C25">
         <v>16.214284896850501</v>
@@ -2385,66 +2722,66 @@
         <v>23</v>
       </c>
       <c r="I25">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="J25">
-        <v>918</v>
+        <v>939</v>
       </c>
       <c r="K25">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="L25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="M25">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="N25">
-        <v>640</v>
+        <v>544</v>
       </c>
       <c r="O25">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="P25">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="Q25">
         <v>1</v>
       </c>
       <c r="R25">
-        <v>13.684972999999999</v>
+        <v>13.561368999999999</v>
       </c>
       <c r="S25" t="s">
         <v>28</v>
       </c>
       <c r="T25">
-        <v>5.9282499999999995E-4</v>
+        <v>2.0904300000000001E-4</v>
       </c>
       <c r="U25" t="s">
         <v>29</v>
       </c>
       <c r="V25">
-        <v>1.3634151000000001E-2</v>
+        <v>1.3527182E-2</v>
       </c>
       <c r="W25">
         <v>14</v>
       </c>
       <c r="X25">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="Y25">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="Z25">
-        <v>918</v>
+        <v>939</v>
       </c>
     </row>
     <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26">
-        <v>0.100087196</v>
+        <v>7.2423873E-2</v>
       </c>
       <c r="B26">
-        <v>2.6637168141592902</v>
+        <v>4.3403057119871198</v>
       </c>
       <c r="C26">
         <v>20.931034088134702</v>
@@ -2456,7 +2793,7 @@
         <v>33</v>
       </c>
       <c r="F26">
-        <v>10105</v>
+        <v>13863</v>
       </c>
       <c r="G26" t="s">
         <v>26</v>
@@ -2465,66 +2802,66 @@
         <v>24</v>
       </c>
       <c r="I26">
-        <v>2641</v>
+        <v>653</v>
       </c>
       <c r="J26">
-        <v>10105</v>
+        <v>15299</v>
       </c>
       <c r="K26">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L26" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M26">
-        <v>1539</v>
+        <v>3221</v>
       </c>
       <c r="N26">
-        <v>3311</v>
+        <v>5395</v>
       </c>
       <c r="O26">
-        <v>1539</v>
+        <v>3221</v>
       </c>
       <c r="P26">
-        <v>2613</v>
+        <v>541</v>
       </c>
       <c r="Q26">
         <v>1</v>
       </c>
       <c r="R26">
-        <v>988.33073899999999</v>
+        <v>357.87298299999998</v>
       </c>
       <c r="S26" t="s">
         <v>28</v>
       </c>
       <c r="T26">
-        <v>0.88694906299999998</v>
+        <v>0.28472052399999997</v>
       </c>
       <c r="U26" t="s">
         <v>29</v>
       </c>
       <c r="V26">
-        <v>0.98703565599999998</v>
+        <v>0.35714386799999998</v>
       </c>
       <c r="W26">
         <v>29</v>
       </c>
       <c r="X26">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="Y26">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="Z26">
-        <v>10105</v>
+        <v>15299</v>
       </c>
     </row>
     <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27">
-        <v>0.22832640300000001</v>
+        <v>5.9515162999999899E-2</v>
       </c>
       <c r="B27">
-        <v>3.7158974358974302</v>
+        <v>5.0092307692307596</v>
       </c>
       <c r="C27">
         <v>19</v>
@@ -2536,7 +2873,7 @@
         <v>33</v>
       </c>
       <c r="F27">
-        <v>7325</v>
+        <v>7920</v>
       </c>
       <c r="G27" t="s">
         <v>26</v>
@@ -2545,66 +2882,66 @@
         <v>25</v>
       </c>
       <c r="I27">
-        <v>3304</v>
+        <v>215</v>
       </c>
       <c r="J27">
-        <v>7325</v>
+        <v>8174</v>
       </c>
       <c r="K27">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L27" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="M27">
-        <v>1946</v>
+        <v>2947</v>
       </c>
       <c r="N27">
-        <v>3623</v>
+        <v>4884</v>
       </c>
       <c r="O27">
-        <v>1946</v>
+        <v>2947</v>
       </c>
       <c r="P27">
-        <v>3219</v>
+        <v>31</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R27">
-        <v>26050.040110999998</v>
+        <v>335.81733300000002</v>
       </c>
       <c r="S27" t="s">
         <v>28</v>
       </c>
       <c r="T27">
-        <v>25.11948778</v>
+        <v>0.27585967500000003</v>
       </c>
       <c r="U27" t="s">
         <v>29</v>
       </c>
       <c r="V27">
-        <v>25.347813477999999</v>
+        <v>0.335374165</v>
       </c>
       <c r="W27">
         <v>25</v>
       </c>
       <c r="X27">
-        <v>69</v>
+        <v>106</v>
       </c>
       <c r="Y27">
-        <v>14</v>
+        <v>74</v>
       </c>
       <c r="Z27">
-        <v>7325</v>
+        <v>8174</v>
       </c>
     </row>
     <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28">
-        <v>4.9931573999999999E-2</v>
+        <v>3.15664599999999E-2</v>
       </c>
       <c r="B28">
-        <v>2.8756830601092802</v>
+        <v>3.3756830601092802</v>
       </c>
       <c r="C28">
         <v>22.375</v>
@@ -2616,7 +2953,7 @@
         <v>33</v>
       </c>
       <c r="F28">
-        <v>2148</v>
+        <v>3714</v>
       </c>
       <c r="G28" t="s">
         <v>26</v>
@@ -2625,66 +2962,66 @@
         <v>26</v>
       </c>
       <c r="I28">
-        <v>1060</v>
+        <v>480</v>
       </c>
       <c r="J28">
-        <v>2148</v>
+        <v>3957</v>
       </c>
       <c r="K28">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="M28">
-        <v>1077</v>
+        <v>1357</v>
       </c>
       <c r="N28">
-        <v>2105</v>
+        <v>2471</v>
       </c>
       <c r="O28">
-        <v>1077</v>
+        <v>1357</v>
       </c>
       <c r="P28">
-        <v>1013</v>
+        <v>396</v>
       </c>
       <c r="Q28">
         <v>1</v>
       </c>
       <c r="R28">
-        <v>530.05376999999999</v>
+        <v>159.74116699999999</v>
       </c>
       <c r="S28" t="s">
         <v>28</v>
       </c>
       <c r="T28">
-        <v>0.47934851099999998</v>
+        <v>0.12778975300000001</v>
       </c>
       <c r="U28" t="s">
         <v>29</v>
       </c>
       <c r="V28">
-        <v>0.52927941899999997</v>
+        <v>0.15935555400000001</v>
       </c>
       <c r="W28">
         <v>16</v>
       </c>
       <c r="X28">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="Y28">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="Z28">
-        <v>2148</v>
+        <v>3957</v>
       </c>
     </row>
     <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29">
-        <v>2.1794278E-2</v>
+        <v>2.1897415E-2</v>
       </c>
       <c r="B29">
-        <v>2.2880434782608599</v>
+        <v>3.35144927536231</v>
       </c>
       <c r="C29">
         <v>19.214284896850501</v>
@@ -2696,7 +3033,7 @@
         <v>33</v>
       </c>
       <c r="F29">
-        <v>2069</v>
+        <v>3531</v>
       </c>
       <c r="G29" t="s">
         <v>26</v>
@@ -2705,61 +3042,67 @@
         <v>27</v>
       </c>
       <c r="I29">
-        <v>402</v>
+        <v>207</v>
       </c>
       <c r="J29">
-        <v>2069</v>
+        <v>3767</v>
       </c>
       <c r="K29">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="L29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="M29">
-        <v>559</v>
+        <v>1057</v>
       </c>
       <c r="N29">
-        <v>1263</v>
+        <v>1850</v>
       </c>
       <c r="O29">
-        <v>559</v>
+        <v>1057</v>
       </c>
       <c r="P29">
-        <v>355</v>
+        <v>90</v>
       </c>
       <c r="Q29">
         <v>1</v>
       </c>
       <c r="R29">
-        <v>54.844056000000002</v>
+        <v>40.197629999999997</v>
       </c>
       <c r="S29" t="s">
         <v>28</v>
       </c>
       <c r="T29">
-        <v>3.2803107999999997E-2</v>
+        <v>1.8082481000000001E-2</v>
       </c>
       <c r="U29" t="s">
         <v>29</v>
       </c>
       <c r="V29">
-        <v>5.4596882999999999E-2</v>
+        <v>3.9979236000000001E-2</v>
       </c>
       <c r="W29">
         <v>14</v>
       </c>
       <c r="X29">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="Y29">
-        <v>22</v>
+        <v>59</v>
       </c>
       <c r="Z29">
-        <v>2069</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A30">
+        <v>1.6336178E-2</v>
+      </c>
+      <c r="B30">
+        <v>1.9915611814345899</v>
+      </c>
       <c r="C30">
         <v>19.25</v>
       </c>
@@ -2769,29 +3112,77 @@
       <c r="E30">
         <v>33</v>
       </c>
+      <c r="F30">
+        <v>3379</v>
+      </c>
       <c r="G30" t="s">
         <v>26</v>
       </c>
       <c r="H30">
         <v>28</v>
       </c>
+      <c r="I30">
+        <v>99</v>
+      </c>
+      <c r="J30">
+        <v>4028</v>
+      </c>
+      <c r="K30">
+        <v>9</v>
+      </c>
       <c r="L30" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="M30">
+        <v>383</v>
+      </c>
+      <c r="N30">
+        <v>944</v>
+      </c>
+      <c r="O30">
+        <v>383</v>
+      </c>
+      <c r="P30">
+        <v>19</v>
+      </c>
+      <c r="Q30">
+        <v>2</v>
       </c>
       <c r="R30">
-        <v>120000</v>
+        <v>21.844605999999999</v>
       </c>
       <c r="S30" t="s">
         <v>28</v>
       </c>
+      <c r="T30">
+        <v>5.4529180000000002E-3</v>
+      </c>
       <c r="U30" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V30">
+        <v>2.1788302999999998E-2</v>
       </c>
       <c r="W30">
         <v>12</v>
       </c>
+      <c r="X30">
+        <v>20</v>
+      </c>
+      <c r="Y30">
+        <v>57</v>
+      </c>
+      <c r="Z30">
+        <v>4028</v>
+      </c>
     </row>
     <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>1.53467639999999E-2</v>
+      </c>
+      <c r="B31">
+        <v>2.1797385620915</v>
+      </c>
       <c r="C31">
         <v>18.625</v>
       </c>
@@ -2801,29 +3192,77 @@
       <c r="E31">
         <v>33</v>
       </c>
+      <c r="F31">
+        <v>1760</v>
+      </c>
       <c r="G31" t="s">
         <v>26</v>
       </c>
       <c r="H31">
         <v>29</v>
       </c>
+      <c r="I31">
+        <v>82</v>
+      </c>
+      <c r="J31">
+        <v>2008</v>
+      </c>
+      <c r="K31">
+        <v>9</v>
+      </c>
       <c r="L31" t="s">
-        <v>60</v>
+        <v>58</v>
+      </c>
+      <c r="M31">
+        <v>303</v>
+      </c>
+      <c r="N31">
+        <v>667</v>
+      </c>
+      <c r="O31">
+        <v>303</v>
+      </c>
+      <c r="P31">
+        <v>12</v>
+      </c>
+      <c r="Q31">
+        <v>1</v>
       </c>
       <c r="R31">
-        <v>120000</v>
+        <v>17.367635</v>
       </c>
       <c r="S31" t="s">
         <v>28</v>
       </c>
+      <c r="T31">
+        <v>1.940916E-3</v>
+      </c>
       <c r="U31" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V31">
+        <v>1.7287132E-2</v>
       </c>
       <c r="W31">
         <v>8</v>
       </c>
+      <c r="X31">
+        <v>12</v>
+      </c>
+      <c r="Y31">
+        <v>56</v>
+      </c>
+      <c r="Z31">
+        <v>2008</v>
+      </c>
     </row>
     <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>1.3038777E-2</v>
+      </c>
+      <c r="B32">
+        <v>2.48571428571428</v>
+      </c>
       <c r="C32">
         <v>12.625</v>
       </c>
@@ -2833,34 +3272,76 @@
       <c r="E32">
         <v>33</v>
       </c>
+      <c r="F32">
+        <v>1828</v>
+      </c>
       <c r="G32" t="s">
         <v>26</v>
       </c>
       <c r="H32">
         <v>30</v>
       </c>
+      <c r="I32">
+        <v>55</v>
+      </c>
+      <c r="J32">
+        <v>1955</v>
+      </c>
+      <c r="K32">
+        <v>8</v>
+      </c>
       <c r="L32" t="s">
-        <v>61</v>
+        <v>59</v>
+      </c>
+      <c r="M32">
+        <v>261</v>
+      </c>
+      <c r="N32">
+        <v>522</v>
+      </c>
+      <c r="O32">
+        <v>261</v>
+      </c>
+      <c r="P32">
+        <v>7</v>
+      </c>
+      <c r="Q32">
+        <v>1</v>
       </c>
       <c r="R32">
-        <v>120000</v>
+        <v>13.906966000000001</v>
       </c>
       <c r="S32" t="s">
         <v>28</v>
       </c>
+      <c r="T32">
+        <v>8.3696300000000003E-4</v>
+      </c>
       <c r="U32" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V32">
+        <v>1.3875181E-2</v>
       </c>
       <c r="W32">
         <v>8</v>
       </c>
+      <c r="X32">
+        <v>10</v>
+      </c>
+      <c r="Y32">
+        <v>36</v>
+      </c>
+      <c r="Z32">
+        <v>1955</v>
+      </c>
     </row>
     <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33">
-        <v>0.33134967300000501</v>
+        <v>0.122173852000003</v>
       </c>
       <c r="B33">
-        <v>5</v>
+        <v>16.313351498637601</v>
       </c>
       <c r="C33">
         <v>19.888889312744102</v>
@@ -2878,66 +3359,66 @@
         <v>31</v>
       </c>
       <c r="I33">
-        <v>3507</v>
+        <v>888</v>
       </c>
       <c r="J33">
-        <v>19418</v>
+        <v>32284</v>
       </c>
       <c r="K33">
-        <v>30</v>
+        <v>110</v>
       </c>
       <c r="L33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="M33">
-        <v>2879</v>
+        <v>11496</v>
       </c>
       <c r="N33">
-        <v>5505</v>
+        <v>17961</v>
       </c>
       <c r="O33">
-        <v>2879</v>
+        <v>11496</v>
       </c>
       <c r="P33">
-        <v>3475</v>
+        <v>722</v>
       </c>
       <c r="Q33">
         <v>1</v>
       </c>
       <c r="R33">
-        <v>120010.84816199999</v>
+        <v>126377.72343100001</v>
       </c>
       <c r="S33" t="s">
         <v>28</v>
       </c>
       <c r="T33">
-        <v>119.679499185</v>
+        <v>126.255550265</v>
       </c>
       <c r="U33" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V33">
-        <v>120.010848162</v>
+        <v>126.37772343100001</v>
       </c>
       <c r="W33">
         <v>27</v>
       </c>
       <c r="X33">
-        <v>31</v>
+        <v>164</v>
       </c>
       <c r="Y33">
         <v>0</v>
       </c>
       <c r="Z33">
-        <v>34696</v>
+        <v>33666</v>
       </c>
     </row>
     <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>0.179789958999998</v>
+        <v>4.5119138000000003E-2</v>
       </c>
       <c r="B34">
-        <v>3.76885644768856</v>
+        <v>4.8783454987834496</v>
       </c>
       <c r="C34">
         <v>20.049999237060501</v>
@@ -2949,7 +3430,7 @@
         <v>33</v>
       </c>
       <c r="F34">
-        <v>6955</v>
+        <v>8061</v>
       </c>
       <c r="G34" t="s">
         <v>26</v>
@@ -2958,61 +3439,67 @@
         <v>32</v>
       </c>
       <c r="I34">
-        <v>2980</v>
+        <v>195</v>
       </c>
       <c r="J34">
-        <v>6955</v>
+        <v>8109</v>
       </c>
       <c r="K34">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="L34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M34">
-        <v>1794</v>
+        <v>2375</v>
       </c>
       <c r="N34">
-        <v>3098</v>
+        <v>4010</v>
       </c>
       <c r="O34">
-        <v>1794</v>
+        <v>2375</v>
       </c>
       <c r="P34">
-        <v>2885</v>
+        <v>90</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>13882.972857000001</v>
+        <v>414.30072100000001</v>
       </c>
       <c r="S34" t="s">
         <v>28</v>
       </c>
       <c r="T34">
-        <v>13.700941369000001</v>
+        <v>0.36805705900000002</v>
       </c>
       <c r="U34" t="s">
         <v>29</v>
       </c>
       <c r="V34">
-        <v>13.88073067</v>
+        <v>0.41317564499999998</v>
       </c>
       <c r="W34">
         <v>20</v>
       </c>
       <c r="X34">
-        <v>66</v>
+        <v>90</v>
       </c>
       <c r="Y34">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="Z34">
-        <v>6955</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>1.9040699000000001E-2</v>
+      </c>
+      <c r="B35">
+        <v>2.3874015748031399</v>
+      </c>
       <c r="C35">
         <v>18.176469802856399</v>
       </c>
@@ -3022,34 +3509,76 @@
       <c r="E35">
         <v>33</v>
       </c>
+      <c r="F35">
+        <v>7511</v>
+      </c>
       <c r="G35" t="s">
         <v>26</v>
       </c>
       <c r="H35">
         <v>33</v>
       </c>
+      <c r="I35">
+        <v>96</v>
+      </c>
+      <c r="J35">
+        <v>8185</v>
+      </c>
+      <c r="K35">
+        <v>10</v>
+      </c>
       <c r="L35" t="s">
-        <v>64</v>
+        <v>63</v>
+      </c>
+      <c r="M35">
+        <v>659</v>
+      </c>
+      <c r="N35">
+        <v>1516</v>
+      </c>
+      <c r="O35">
+        <v>659</v>
+      </c>
+      <c r="P35">
+        <v>15</v>
+      </c>
+      <c r="Q35">
+        <v>1</v>
       </c>
       <c r="R35">
-        <v>120000</v>
+        <v>26.654786999999999</v>
       </c>
       <c r="S35" t="s">
         <v>28</v>
       </c>
+      <c r="T35">
+        <v>5.7665870000000001E-3</v>
+      </c>
       <c r="U35" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V35">
+        <v>2.4806781E-2</v>
       </c>
       <c r="W35">
         <v>17</v>
       </c>
+      <c r="X35">
+        <v>29</v>
+      </c>
+      <c r="Y35">
+        <v>50</v>
+      </c>
+      <c r="Z35">
+        <v>8185</v>
+      </c>
     </row>
     <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>0.63441201900000899</v>
+        <v>7.7557447000003693E-2</v>
       </c>
       <c r="B36">
-        <v>5.3672966310599799</v>
+        <v>11.806902218570199</v>
       </c>
       <c r="C36">
         <v>20.482759475708001</v>
@@ -3067,52 +3596,52 @@
         <v>34</v>
       </c>
       <c r="I36">
-        <v>5429</v>
+        <v>105</v>
       </c>
       <c r="J36">
-        <v>6215</v>
+        <v>14335</v>
       </c>
       <c r="K36">
+        <v>132</v>
+      </c>
+      <c r="L36" t="s">
         <v>64</v>
       </c>
-      <c r="L36" t="s">
-        <v>65</v>
-      </c>
       <c r="M36">
-        <v>3616</v>
+        <v>9014</v>
       </c>
       <c r="N36">
-        <v>6532</v>
+        <v>14369</v>
       </c>
       <c r="O36">
-        <v>3616</v>
+        <v>9014</v>
       </c>
       <c r="P36">
-        <v>5394</v>
+        <v>22</v>
       </c>
       <c r="Q36">
         <v>1</v>
       </c>
       <c r="R36">
-        <v>120039.100662</v>
+        <v>131024.674900999</v>
       </c>
       <c r="S36" t="s">
         <v>28</v>
       </c>
       <c r="T36">
-        <v>119.40468933</v>
+        <v>130.94711805599999</v>
       </c>
       <c r="U36" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V36">
-        <v>120.039100662</v>
+        <v>131.024674901</v>
       </c>
       <c r="W36">
         <v>29</v>
       </c>
       <c r="X36">
-        <v>34</v>
+        <v>81</v>
       </c>
       <c r="Y36">
         <v>0</v>
@@ -3123,10 +3652,10 @@
     </row>
     <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37">
-        <v>0.506011753000009</v>
+        <v>7.5543757999994895E-2</v>
       </c>
       <c r="B37">
-        <v>5.0434083601286099</v>
+        <v>9.1479099678456599</v>
       </c>
       <c r="C37">
         <v>21.714284896850501</v>
@@ -3144,52 +3673,52 @@
         <v>35</v>
       </c>
       <c r="I37">
-        <v>4576</v>
+        <v>392</v>
       </c>
       <c r="J37">
-        <v>6481</v>
+        <v>12236</v>
       </c>
       <c r="K37">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="L37" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="M37">
-        <v>3321</v>
+        <v>6248</v>
       </c>
       <c r="N37">
-        <v>6274</v>
+        <v>11380</v>
       </c>
       <c r="O37">
-        <v>3321</v>
+        <v>6248</v>
       </c>
       <c r="P37">
-        <v>4545</v>
+        <v>335</v>
       </c>
       <c r="Q37">
         <v>1</v>
       </c>
       <c r="R37">
-        <v>120020.473298</v>
+        <v>121578.287254</v>
       </c>
       <c r="S37" t="s">
         <v>28</v>
       </c>
       <c r="T37">
-        <v>119.514462329</v>
+        <v>121.50274408</v>
       </c>
       <c r="U37" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V37">
-        <v>120.020473298</v>
+        <v>121.578287254</v>
       </c>
       <c r="W37">
         <v>28</v>
       </c>
       <c r="X37">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="Y37">
         <v>0</v>
@@ -3200,10 +3729,10 @@
     </row>
     <row r="38" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A38">
-        <v>3.3397830999999899E-2</v>
+        <v>2.2885943999999998E-2</v>
       </c>
       <c r="B38">
-        <v>2.4984423676012399</v>
+        <v>2.6417445482866002</v>
       </c>
       <c r="C38">
         <v>17.3333339691162</v>
@@ -3215,7 +3744,7 @@
         <v>25</v>
       </c>
       <c r="F38">
-        <v>1507</v>
+        <v>2825</v>
       </c>
       <c r="G38" t="s">
         <v>26</v>
@@ -3224,66 +3753,66 @@
         <v>36</v>
       </c>
       <c r="I38">
-        <v>759</v>
+        <v>200</v>
       </c>
       <c r="J38">
-        <v>1507</v>
+        <v>3015</v>
       </c>
       <c r="K38">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M38">
-        <v>735</v>
+        <v>835</v>
       </c>
       <c r="N38">
-        <v>1604</v>
+        <v>1696</v>
       </c>
       <c r="O38">
-        <v>735</v>
+        <v>835</v>
       </c>
       <c r="P38">
-        <v>720</v>
+        <v>127</v>
       </c>
       <c r="Q38">
         <v>1</v>
       </c>
       <c r="R38">
-        <v>215.11202</v>
+        <v>64.629109999999997</v>
       </c>
       <c r="S38" t="s">
         <v>28</v>
       </c>
       <c r="T38">
-        <v>0.181326921</v>
+        <v>4.1513119000000001E-2</v>
       </c>
       <c r="U38" t="s">
         <v>29</v>
       </c>
       <c r="V38">
-        <v>0.21472411899999999</v>
+        <v>6.4398517000000002E-2</v>
       </c>
       <c r="W38">
         <v>18</v>
       </c>
       <c r="X38">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="Y38">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="Z38">
-        <v>1507</v>
+        <v>3015</v>
       </c>
     </row>
     <row r="39" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A39">
-        <v>1.5369077E-2</v>
+        <v>1.4537148999999999E-2</v>
       </c>
       <c r="B39">
-        <v>1.9019607843137201</v>
+        <v>1.8300653594771199</v>
       </c>
       <c r="C39">
         <v>14.800000190734799</v>
@@ -3304,66 +3833,66 @@
         <v>37</v>
       </c>
       <c r="I39">
-        <v>199</v>
+        <v>73</v>
       </c>
       <c r="J39">
-        <v>4404</v>
+        <v>4528</v>
       </c>
       <c r="K39">
         <v>5</v>
       </c>
       <c r="L39" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M39">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="N39">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="O39">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="P39">
-        <v>153</v>
+        <v>35</v>
       </c>
       <c r="Q39">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R39">
-        <v>20.715636</v>
+        <v>16.194979</v>
       </c>
       <c r="S39" t="s">
         <v>28</v>
       </c>
       <c r="T39">
-        <v>5.2462660000000003E-3</v>
+        <v>1.6028259999999999E-3</v>
       </c>
       <c r="U39" t="s">
         <v>29</v>
       </c>
       <c r="V39">
-        <v>2.0614852999999999E-2</v>
+        <v>1.6139461000000001E-2</v>
       </c>
       <c r="W39">
         <v>5</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y39">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="Z39">
-        <v>4404</v>
+        <v>4528</v>
       </c>
     </row>
     <row r="40" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A40">
-        <v>1.5307194999999999E-2</v>
+        <v>1.4142745999999999E-2</v>
       </c>
       <c r="B40">
-        <v>3.0751445086705198</v>
+        <v>3.7398843930635799</v>
       </c>
       <c r="C40">
         <v>16.799999237060501</v>
@@ -3375,7 +3904,7 @@
         <v>20</v>
       </c>
       <c r="F40">
-        <v>596</v>
+        <v>666</v>
       </c>
       <c r="G40" t="s">
         <v>26</v>
@@ -3384,66 +3913,66 @@
         <v>38</v>
       </c>
       <c r="I40">
-        <v>162</v>
+        <v>84</v>
       </c>
       <c r="J40">
-        <v>596</v>
+        <v>732</v>
       </c>
       <c r="K40">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L40" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M40">
-        <v>273</v>
+        <v>378</v>
       </c>
       <c r="N40">
-        <v>532</v>
+        <v>647</v>
       </c>
       <c r="O40">
-        <v>273</v>
+        <v>378</v>
       </c>
       <c r="P40">
-        <v>103</v>
+        <v>14</v>
       </c>
       <c r="Q40">
         <v>1</v>
       </c>
       <c r="R40">
-        <v>20.236184000000002</v>
+        <v>16.182276000000002</v>
       </c>
       <c r="S40" t="s">
         <v>28</v>
       </c>
       <c r="T40">
-        <v>4.8567580000000001E-3</v>
+        <v>2.0055089999999999E-3</v>
       </c>
       <c r="U40" t="s">
         <v>29</v>
       </c>
       <c r="V40">
-        <v>2.0163361000000001E-2</v>
+        <v>1.6147659000000002E-2</v>
       </c>
       <c r="W40">
         <v>5</v>
       </c>
       <c r="X40">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="Y40">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="Z40">
-        <v>596</v>
+        <v>732</v>
       </c>
     </row>
     <row r="41" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A41">
-        <v>0.18839798399999899</v>
+        <v>3.2709428999999998E-2</v>
       </c>
       <c r="B41">
-        <v>4.01671732522796</v>
+        <v>4.5303951367781101</v>
       </c>
       <c r="C41">
         <v>15.949999809265099</v>
@@ -3455,7 +3984,7 @@
         <v>25</v>
       </c>
       <c r="F41">
-        <v>61031</v>
+        <v>64015</v>
       </c>
       <c r="G41" t="s">
         <v>26</v>
@@ -3464,66 +3993,66 @@
         <v>39</v>
       </c>
       <c r="I41">
-        <v>2803</v>
+        <v>159</v>
       </c>
       <c r="J41">
-        <v>61031</v>
+        <v>65494</v>
       </c>
       <c r="K41">
         <v>29</v>
       </c>
       <c r="L41" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M41">
-        <v>1489</v>
+        <v>1774</v>
       </c>
       <c r="N41">
-        <v>2643</v>
+        <v>2981</v>
       </c>
       <c r="O41">
-        <v>1489</v>
+        <v>1774</v>
       </c>
       <c r="P41">
-        <v>2736</v>
+        <v>13</v>
       </c>
       <c r="Q41">
         <v>1</v>
       </c>
       <c r="R41">
-        <v>14857.447713</v>
+        <v>105.528071</v>
       </c>
       <c r="S41" t="s">
         <v>28</v>
       </c>
       <c r="T41">
-        <v>14.665358144000001</v>
+        <v>7.2396910999999994E-2</v>
       </c>
       <c r="U41" t="s">
         <v>29</v>
       </c>
       <c r="V41">
-        <v>14.853755565</v>
+        <v>0.10510575699999999</v>
       </c>
       <c r="W41">
         <v>20</v>
       </c>
       <c r="X41">
-        <v>61</v>
+        <v>98</v>
       </c>
       <c r="Y41">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="Z41">
-        <v>61031</v>
+        <v>65494</v>
       </c>
     </row>
     <row r="42" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A42">
-        <v>3.1303359000000003E-2</v>
+        <v>2.2022962999999899E-2</v>
       </c>
       <c r="B42">
-        <v>3.1202185792349701</v>
+        <v>3.9398907103825098</v>
       </c>
       <c r="C42">
         <v>17.799999237060501</v>
@@ -3544,66 +4073,66 @@
         <v>40</v>
       </c>
       <c r="I42">
-        <v>807</v>
+        <v>347</v>
       </c>
       <c r="J42">
-        <v>1930</v>
+        <v>1949</v>
       </c>
       <c r="K42">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L42" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="M42">
-        <v>306</v>
+        <v>415</v>
       </c>
       <c r="N42">
-        <v>571</v>
+        <v>721</v>
       </c>
       <c r="O42">
-        <v>306</v>
+        <v>415</v>
       </c>
       <c r="P42">
-        <v>757</v>
+        <v>263</v>
       </c>
       <c r="Q42">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R42">
-        <v>113.97463500000001</v>
+        <v>50.003058000000003</v>
       </c>
       <c r="S42" t="s">
         <v>28</v>
       </c>
       <c r="T42">
-        <v>8.2262163999999999E-2</v>
+        <v>2.7697623000000001E-2</v>
       </c>
       <c r="U42" t="s">
         <v>29</v>
       </c>
       <c r="V42">
-        <v>0.113564993</v>
+        <v>4.9719458000000001E-2</v>
       </c>
       <c r="W42">
         <v>5</v>
       </c>
       <c r="X42">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="Y42">
-        <v>33</v>
+        <v>50</v>
       </c>
       <c r="Z42">
-        <v>1930</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="43" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A43">
-        <v>1.2142725E-2</v>
+        <v>1.3890435E-2</v>
       </c>
       <c r="B43">
-        <v>1.5605095541401199</v>
+        <v>1.76433121019108</v>
       </c>
       <c r="C43">
         <v>15.199999809265099</v>
@@ -3624,46 +4153,46 @@
         <v>41</v>
       </c>
       <c r="I43">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="J43">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="K43">
         <v>4</v>
       </c>
       <c r="L43" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M43">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="N43">
-        <v>245</v>
+        <v>277</v>
       </c>
       <c r="O43">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="P43">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q43">
         <v>1</v>
       </c>
       <c r="R43">
-        <v>12.284203</v>
+        <v>14.149172</v>
       </c>
       <c r="S43" t="s">
         <v>28</v>
       </c>
       <c r="T43">
-        <v>1.21206E-4</v>
+        <v>1.9389900000000001E-4</v>
       </c>
       <c r="U43" t="s">
         <v>29</v>
       </c>
       <c r="V43">
-        <v>1.2263309E-2</v>
+        <v>1.4083869000000001E-2</v>
       </c>
       <c r="W43">
         <v>5</v>
@@ -3672,18 +4201,18 @@
         <v>2</v>
       </c>
       <c r="Y43">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="Z43">
-        <v>209</v>
+        <v>217</v>
       </c>
     </row>
     <row r="44" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A44">
-        <v>0.185874132999998</v>
+        <v>2.6796692E-2</v>
       </c>
       <c r="B44">
-        <v>2.1494708994708902</v>
+        <v>3.6084656084655999</v>
       </c>
       <c r="C44">
         <v>15.25</v>
@@ -3695,7 +4224,7 @@
         <v>25</v>
       </c>
       <c r="F44">
-        <v>56190</v>
+        <v>61645</v>
       </c>
       <c r="G44" t="s">
         <v>26</v>
@@ -3704,61 +4233,67 @@
         <v>42</v>
       </c>
       <c r="I44">
-        <v>2622</v>
+        <v>126</v>
       </c>
       <c r="J44">
-        <v>56190</v>
+        <v>62206</v>
       </c>
       <c r="K44">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L44" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="M44">
-        <v>631</v>
+        <v>1531</v>
       </c>
       <c r="N44">
-        <v>1625</v>
+        <v>2728</v>
       </c>
       <c r="O44">
-        <v>631</v>
+        <v>1531</v>
       </c>
       <c r="P44">
-        <v>2596</v>
+        <v>12</v>
       </c>
       <c r="Q44">
         <v>1</v>
       </c>
       <c r="R44">
-        <v>23547.402196999999</v>
+        <v>65.874249000000006</v>
       </c>
       <c r="S44" t="s">
         <v>28</v>
       </c>
       <c r="T44">
-        <v>22.646337659</v>
+        <v>3.8706602E-2</v>
       </c>
       <c r="U44" t="s">
         <v>29</v>
       </c>
       <c r="V44">
-        <v>22.832211130000001</v>
+        <v>6.5502788000000006E-2</v>
       </c>
       <c r="W44">
         <v>24</v>
       </c>
       <c r="X44">
-        <v>22</v>
+        <v>67</v>
       </c>
       <c r="Y44">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="Z44">
-        <v>56190</v>
+        <v>62206</v>
       </c>
     </row>
     <row r="45" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>1.3935512000000001E-2</v>
+      </c>
+      <c r="B45">
+        <v>2.2374100719424401</v>
+      </c>
       <c r="C45">
         <v>13.399999618530201</v>
       </c>
@@ -3768,29 +4303,77 @@
       <c r="E45">
         <v>25</v>
       </c>
+      <c r="F45">
+        <v>2468</v>
+      </c>
       <c r="G45" t="s">
         <v>26</v>
       </c>
       <c r="H45">
         <v>43</v>
       </c>
+      <c r="I45">
+        <v>76</v>
+      </c>
+      <c r="J45">
+        <v>2747</v>
+      </c>
+      <c r="K45">
+        <v>6</v>
+      </c>
       <c r="L45" t="s">
-        <v>74</v>
+        <v>73</v>
+      </c>
+      <c r="M45">
+        <v>142</v>
+      </c>
+      <c r="N45">
+        <v>311</v>
+      </c>
+      <c r="O45">
+        <v>142</v>
+      </c>
+      <c r="P45">
+        <v>27</v>
+      </c>
+      <c r="Q45">
+        <v>1</v>
       </c>
       <c r="R45">
-        <v>120000</v>
+        <v>15.952692000000001</v>
       </c>
       <c r="S45" t="s">
         <v>28</v>
       </c>
+      <c r="T45">
+        <v>1.9617609999999998E-3</v>
+      </c>
       <c r="U45" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V45">
+        <v>1.5896687E-2</v>
       </c>
       <c r="W45">
         <v>5</v>
       </c>
+      <c r="X45">
+        <v>7</v>
+      </c>
+      <c r="Y45">
+        <v>40</v>
+      </c>
+      <c r="Z45">
+        <v>2747</v>
+      </c>
     </row>
     <row r="46" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>1.5376249999999999E-2</v>
+      </c>
+      <c r="B46">
+        <v>4.3401015228426303</v>
+      </c>
       <c r="C46">
         <v>13.571428298950099</v>
       </c>
@@ -3800,34 +4383,76 @@
       <c r="E46">
         <v>25</v>
       </c>
+      <c r="F46">
+        <v>10822</v>
+      </c>
       <c r="G46" t="s">
         <v>26</v>
       </c>
       <c r="H46">
         <v>44</v>
       </c>
+      <c r="I46">
+        <v>84</v>
+      </c>
+      <c r="J46">
+        <v>16121</v>
+      </c>
+      <c r="K46">
+        <v>15</v>
+      </c>
       <c r="L46" t="s">
-        <v>75</v>
+        <v>74</v>
+      </c>
+      <c r="M46">
+        <v>457</v>
+      </c>
+      <c r="N46">
+        <v>855</v>
+      </c>
+      <c r="O46">
+        <v>457</v>
+      </c>
+      <c r="P46">
+        <v>11</v>
+      </c>
+      <c r="Q46">
+        <v>2</v>
       </c>
       <c r="R46">
-        <v>120000</v>
+        <v>18.033669</v>
       </c>
       <c r="S46" t="s">
         <v>28</v>
       </c>
+      <c r="T46">
+        <v>2.5703940000000002E-3</v>
+      </c>
       <c r="U46" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V46">
+        <v>1.7946086E-2</v>
       </c>
       <c r="W46">
         <v>7</v>
       </c>
+      <c r="X46">
+        <v>38</v>
+      </c>
+      <c r="Y46">
+        <v>32</v>
+      </c>
+      <c r="Z46">
+        <v>16121</v>
+      </c>
     </row>
     <row r="47" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A47">
-        <v>1.41018569999999E-2</v>
+        <v>1.2748844E-2</v>
       </c>
       <c r="B47">
-        <v>1.5882352941176401</v>
+        <v>1.57754010695187</v>
       </c>
       <c r="C47">
         <v>12.857142448425201</v>
@@ -3848,46 +4473,46 @@
         <v>45</v>
       </c>
       <c r="I47">
-        <v>143</v>
+        <v>52</v>
       </c>
       <c r="J47">
-        <v>6912</v>
+        <v>6992</v>
       </c>
       <c r="K47">
         <v>3</v>
       </c>
       <c r="L47" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M47">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N47">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="O47">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="P47">
-        <v>107</v>
+        <v>11</v>
       </c>
       <c r="Q47">
         <v>1</v>
       </c>
       <c r="R47">
-        <v>17.132612999999999</v>
+        <v>13.364872999999999</v>
       </c>
       <c r="S47" t="s">
         <v>28</v>
       </c>
       <c r="T47">
-        <v>2.9734140000000002E-3</v>
+        <v>5.78368E-4</v>
       </c>
       <c r="U47" t="s">
         <v>29</v>
       </c>
       <c r="V47">
-        <v>1.7074684999999999E-2</v>
+        <v>1.3326595E-2</v>
       </c>
       <c r="W47">
         <v>7</v>
@@ -3896,13 +4521,19 @@
         <v>2</v>
       </c>
       <c r="Y47">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="Z47">
-        <v>6912</v>
+        <v>6992</v>
       </c>
     </row>
     <row r="48" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>4.6061393999999999E-2</v>
+      </c>
+      <c r="B48">
+        <v>2.3584905660377302</v>
+      </c>
       <c r="C48">
         <v>15.399999618530201</v>
       </c>
@@ -3912,34 +4543,76 @@
       <c r="E48">
         <v>25</v>
       </c>
+      <c r="F48">
+        <v>77250</v>
+      </c>
       <c r="G48" t="s">
         <v>26</v>
       </c>
       <c r="H48">
         <v>46</v>
       </c>
+      <c r="I48">
+        <v>1039</v>
+      </c>
+      <c r="J48">
+        <v>125934</v>
+      </c>
+      <c r="K48">
+        <v>10</v>
+      </c>
       <c r="L48" t="s">
-        <v>77</v>
+        <v>76</v>
+      </c>
+      <c r="M48">
+        <v>780</v>
+      </c>
+      <c r="N48">
+        <v>1875</v>
+      </c>
+      <c r="O48">
+        <v>780</v>
+      </c>
+      <c r="P48">
+        <v>980</v>
+      </c>
+      <c r="Q48">
+        <v>1</v>
       </c>
       <c r="R48">
-        <v>120000</v>
+        <v>184.487899</v>
       </c>
       <c r="S48" t="s">
         <v>28</v>
       </c>
+      <c r="T48">
+        <v>0.13770672</v>
+      </c>
       <c r="U48" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V48">
+        <v>0.183767598</v>
       </c>
       <c r="W48">
         <v>25</v>
       </c>
+      <c r="X48">
+        <v>38</v>
+      </c>
+      <c r="Y48">
+        <v>19</v>
+      </c>
+      <c r="Z48">
+        <v>125934</v>
+      </c>
     </row>
     <row r="49" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A49">
-        <v>0.314990203999999</v>
+        <v>0.16754612999999899</v>
       </c>
       <c r="B49">
-        <v>2.2286324786324698</v>
+        <v>3.0170940170940099</v>
       </c>
       <c r="C49">
         <v>16.214284896850501</v>
@@ -3951,7 +4624,7 @@
         <v>25</v>
       </c>
       <c r="F49">
-        <v>19676</v>
+        <v>26946</v>
       </c>
       <c r="G49" t="s">
         <v>26</v>
@@ -3960,66 +4633,66 @@
         <v>47</v>
       </c>
       <c r="I49">
-        <v>6563</v>
+        <v>3367</v>
       </c>
       <c r="J49">
-        <v>19676</v>
+        <v>27328</v>
       </c>
       <c r="K49">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L49" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M49">
-        <v>362</v>
+        <v>684</v>
       </c>
       <c r="N49">
-        <v>1043</v>
+        <v>1412</v>
       </c>
       <c r="O49">
-        <v>362</v>
+        <v>684</v>
       </c>
       <c r="P49">
-        <v>6540</v>
+        <v>3304</v>
       </c>
       <c r="Q49">
         <v>1</v>
       </c>
       <c r="R49">
-        <v>5447.4513809999999</v>
+        <v>2173.6010339999998</v>
       </c>
       <c r="S49" t="s">
         <v>28</v>
       </c>
       <c r="T49">
-        <v>5.1294860980000001</v>
+        <v>2.0031389580000001</v>
       </c>
       <c r="U49" t="s">
         <v>29</v>
       </c>
       <c r="V49">
-        <v>5.4444756959999996</v>
+        <v>2.170684477</v>
       </c>
       <c r="W49">
         <v>14</v>
       </c>
       <c r="X49">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="Y49">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="Z49">
-        <v>19676</v>
+        <v>27328</v>
       </c>
     </row>
     <row r="50" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>0.36219696599999901</v>
+        <v>8.9095710999999606E-2</v>
       </c>
       <c r="B50">
-        <v>3.87288817377312</v>
+        <v>5.8294448913917902</v>
       </c>
       <c r="C50">
         <v>20.931034088134702</v>
@@ -4030,6 +4703,9 @@
       <c r="E50">
         <v>33</v>
       </c>
+      <c r="F50">
+        <v>14747</v>
+      </c>
       <c r="G50" t="s">
         <v>26</v>
       </c>
@@ -4037,66 +4713,66 @@
         <v>48</v>
       </c>
       <c r="I50">
-        <v>4372</v>
+        <v>530</v>
       </c>
       <c r="J50">
-        <v>12085</v>
+        <v>15384</v>
       </c>
       <c r="K50">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="L50" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M50">
-        <v>2689</v>
+        <v>4572</v>
       </c>
       <c r="N50">
-        <v>4814</v>
+        <v>7246</v>
       </c>
       <c r="O50">
-        <v>2689</v>
+        <v>4572</v>
       </c>
       <c r="P50">
-        <v>4329</v>
+        <v>350</v>
       </c>
       <c r="Q50">
         <v>1</v>
       </c>
       <c r="R50">
-        <v>120237.497043999</v>
+        <v>7432.6167519999999</v>
       </c>
       <c r="S50" t="s">
         <v>28</v>
       </c>
       <c r="T50">
-        <v>119.875300659</v>
+        <v>7.3426809850000003</v>
       </c>
       <c r="U50" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="V50">
-        <v>120.23749704399999</v>
+        <v>7.4317759519999997</v>
       </c>
       <c r="W50">
         <v>29</v>
       </c>
       <c r="X50">
-        <v>42</v>
+        <v>127</v>
       </c>
       <c r="Y50">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="Z50">
-        <v>14121</v>
+        <v>15384</v>
       </c>
     </row>
     <row r="51" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A51">
-        <v>0.44209715800000898</v>
+        <v>0.10272830199999899</v>
       </c>
       <c r="B51">
-        <v>4.0461538461538398</v>
+        <v>10.3682051282051</v>
       </c>
       <c r="C51">
         <v>19</v>
@@ -4107,6 +4783,9 @@
       <c r="E51">
         <v>33</v>
       </c>
+      <c r="F51">
+        <v>12524</v>
+      </c>
       <c r="G51" t="s">
         <v>26</v>
       </c>
@@ -4114,66 +4793,66 @@
         <v>49</v>
       </c>
       <c r="I51">
-        <v>4481</v>
+        <v>307</v>
       </c>
       <c r="J51">
-        <v>8694</v>
+        <v>16366</v>
       </c>
       <c r="K51">
-        <v>25</v>
+        <v>62</v>
       </c>
       <c r="L51" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M51">
-        <v>2034</v>
+        <v>6565</v>
       </c>
       <c r="N51">
-        <v>3945</v>
+        <v>10109</v>
       </c>
       <c r="O51">
-        <v>2034</v>
+        <v>6565</v>
       </c>
       <c r="P51">
-        <v>4438</v>
+        <v>38</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="R51">
-        <v>120047.499046</v>
+        <v>5430.2187210000002</v>
       </c>
       <c r="S51" t="s">
         <v>28</v>
       </c>
       <c r="T51">
-        <v>119.60540263599999</v>
+        <v>7.0212364340000004</v>
       </c>
       <c r="U51" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="V51">
-        <v>120.047499046</v>
+        <v>7.1239640849999999</v>
       </c>
       <c r="W51">
         <v>25</v>
       </c>
       <c r="X51">
-        <v>42</v>
+        <v>253</v>
       </c>
       <c r="Y51">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Z51">
-        <v>9974</v>
+        <v>16366</v>
       </c>
     </row>
     <row r="52" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A52">
-        <v>0.14101323399999899</v>
+        <v>2.9057419000000001E-2</v>
       </c>
       <c r="B52">
-        <v>3.0136612021857898</v>
+        <v>3.4207650273224002</v>
       </c>
       <c r="C52">
         <v>22.375</v>
@@ -4185,7 +4864,7 @@
         <v>33</v>
       </c>
       <c r="F52">
-        <v>3730</v>
+        <v>5579</v>
       </c>
       <c r="G52" t="s">
         <v>26</v>
@@ -4194,66 +4873,66 @@
         <v>50</v>
       </c>
       <c r="I52">
-        <v>2419</v>
+        <v>258</v>
       </c>
       <c r="J52">
-        <v>3730</v>
+        <v>8109</v>
       </c>
       <c r="K52">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L52" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M52">
-        <v>1175</v>
+        <v>1424</v>
       </c>
       <c r="N52">
-        <v>2206</v>
+        <v>2504</v>
       </c>
       <c r="O52">
-        <v>1175</v>
+        <v>1424</v>
       </c>
       <c r="P52">
-        <v>2365</v>
+        <v>153</v>
       </c>
       <c r="Q52">
         <v>1</v>
       </c>
       <c r="R52">
-        <v>20430.075140000001</v>
+        <v>609.84281399999998</v>
       </c>
       <c r="S52" t="s">
         <v>28</v>
       </c>
       <c r="T52">
-        <v>20.285649341999999</v>
+        <v>0.58046179099999995</v>
       </c>
       <c r="U52" t="s">
         <v>29</v>
       </c>
       <c r="V52">
-        <v>20.426661272</v>
+        <v>0.60951831999999995</v>
       </c>
       <c r="W52">
         <v>16</v>
       </c>
       <c r="X52">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="Y52">
-        <v>10</v>
+        <v>42</v>
       </c>
       <c r="Z52">
-        <v>3730</v>
+        <v>8109</v>
       </c>
     </row>
     <row r="53" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A53">
-        <v>7.4889992999999905E-2</v>
+        <v>2.3088261999999998E-2</v>
       </c>
       <c r="B53">
-        <v>3.2789855072463698</v>
+        <v>3.0344202898550701</v>
       </c>
       <c r="C53">
         <v>19.214284896850501</v>
@@ -4265,7 +4944,7 @@
         <v>33</v>
       </c>
       <c r="F53">
-        <v>3471</v>
+        <v>3439</v>
       </c>
       <c r="G53" t="s">
         <v>26</v>
@@ -4274,66 +4953,66 @@
         <v>51</v>
       </c>
       <c r="I53">
-        <v>1847</v>
+        <v>327</v>
       </c>
       <c r="J53">
-        <v>3471</v>
+        <v>4023</v>
       </c>
       <c r="K53">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="L53" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M53">
-        <v>1043</v>
+        <v>920</v>
       </c>
       <c r="N53">
-        <v>1810</v>
+        <v>1675</v>
       </c>
       <c r="O53">
-        <v>1043</v>
+        <v>920</v>
       </c>
       <c r="P53">
-        <v>1693</v>
+        <v>223</v>
       </c>
       <c r="Q53">
         <v>1</v>
       </c>
       <c r="R53">
-        <v>964.90360099999998</v>
+        <v>123.012198</v>
       </c>
       <c r="S53" t="s">
         <v>28</v>
       </c>
       <c r="T53">
-        <v>0.88904829299999999</v>
+        <v>9.9671330000000002E-2</v>
       </c>
       <c r="U53" t="s">
         <v>29</v>
       </c>
       <c r="V53">
-        <v>0.96393766700000005</v>
+        <v>0.122758855</v>
       </c>
       <c r="W53">
         <v>14</v>
       </c>
       <c r="X53">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="Y53">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="Z53">
-        <v>3471</v>
+        <v>4023</v>
       </c>
     </row>
     <row r="54" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A54">
-        <v>7.2846990000000097E-2</v>
+        <v>2.0384764999999999E-2</v>
       </c>
       <c r="B54">
-        <v>2.7953586497890202</v>
+        <v>3.6413502109704599</v>
       </c>
       <c r="C54">
         <v>19.25</v>
@@ -4345,7 +5024,7 @@
         <v>33</v>
       </c>
       <c r="F54">
-        <v>3306</v>
+        <v>3911</v>
       </c>
       <c r="G54" t="s">
         <v>26</v>
@@ -4354,66 +5033,66 @@
         <v>52</v>
       </c>
       <c r="I54">
-        <v>1595</v>
+        <v>118</v>
       </c>
       <c r="J54">
-        <v>3306</v>
+        <v>4086</v>
       </c>
       <c r="K54">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L54" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M54">
-        <v>653</v>
+        <v>990</v>
       </c>
       <c r="N54">
-        <v>1325</v>
+        <v>1726</v>
       </c>
       <c r="O54">
-        <v>653</v>
+        <v>990</v>
       </c>
       <c r="P54">
-        <v>1547</v>
+        <v>15</v>
       </c>
       <c r="Q54">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R54">
-        <v>1369.4868409999999</v>
+        <v>46.827880999999998</v>
       </c>
       <c r="S54" t="s">
         <v>28</v>
       </c>
       <c r="T54">
-        <v>1.2953678179999999</v>
+        <v>2.6258488999999999E-2</v>
       </c>
       <c r="U54" t="s">
         <v>29</v>
       </c>
       <c r="V54">
-        <v>1.3682141459999999</v>
+        <v>4.6642457999999998E-2</v>
       </c>
       <c r="W54">
         <v>12</v>
       </c>
       <c r="X54">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="Y54">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="Z54">
-        <v>3306</v>
+        <v>4086</v>
       </c>
     </row>
     <row r="55" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A55">
-        <v>1.7645543999999999E-2</v>
+        <v>1.5063613999999999E-2</v>
       </c>
       <c r="B55">
-        <v>2.05555555555555</v>
+        <v>2.0882352941176401</v>
       </c>
       <c r="C55">
         <v>18.625</v>
@@ -4425,7 +5104,7 @@
         <v>33</v>
       </c>
       <c r="F55">
-        <v>2149</v>
+        <v>3463</v>
       </c>
       <c r="G55" t="s">
         <v>26</v>
@@ -4434,66 +5113,66 @@
         <v>53</v>
       </c>
       <c r="I55">
-        <v>288</v>
+        <v>86</v>
       </c>
       <c r="J55">
-        <v>2149</v>
+        <v>4081</v>
       </c>
       <c r="K55">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L55" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M55">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="N55">
-        <v>629</v>
+        <v>639</v>
       </c>
       <c r="O55">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="P55">
-        <v>249</v>
+        <v>15</v>
       </c>
       <c r="Q55">
         <v>1</v>
       </c>
       <c r="R55">
-        <v>28.269048999999999</v>
+        <v>17.298099000000001</v>
       </c>
       <c r="S55" t="s">
         <v>28</v>
       </c>
       <c r="T55">
-        <v>1.0499614000000001E-2</v>
+        <v>2.1511019999999998E-3</v>
       </c>
       <c r="U55" t="s">
         <v>29</v>
       </c>
       <c r="V55">
-        <v>2.8144582000000001E-2</v>
+        <v>1.7214091000000001E-2</v>
       </c>
       <c r="W55">
         <v>8</v>
       </c>
       <c r="X55">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="Y55">
-        <v>31</v>
+        <v>50</v>
       </c>
       <c r="Z55">
-        <v>2149</v>
+        <v>4081</v>
       </c>
     </row>
     <row r="56" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A56">
-        <v>2.79462459999999E-2</v>
+        <v>1.4234735E-2</v>
       </c>
       <c r="B56">
-        <v>2.48571428571428</v>
+        <v>2.5571428571428498</v>
       </c>
       <c r="C56">
         <v>12.625</v>
@@ -4505,7 +5184,7 @@
         <v>33</v>
       </c>
       <c r="F56">
-        <v>1762</v>
+        <v>2550</v>
       </c>
       <c r="G56" t="s">
         <v>26</v>
@@ -4514,46 +5193,46 @@
         <v>54</v>
       </c>
       <c r="I56">
-        <v>735</v>
+        <v>88</v>
       </c>
       <c r="J56">
-        <v>1762</v>
+        <v>3005</v>
       </c>
       <c r="K56">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L56" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M56">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="N56">
-        <v>522</v>
+        <v>537</v>
       </c>
       <c r="O56">
-        <v>255</v>
+        <v>274</v>
       </c>
       <c r="P56">
-        <v>689</v>
+        <v>16</v>
       </c>
       <c r="Q56">
         <v>1</v>
       </c>
       <c r="R56">
-        <v>99.043063000000004</v>
+        <v>17.685012</v>
       </c>
       <c r="S56" t="s">
         <v>28</v>
       </c>
       <c r="T56">
-        <v>7.0787555000000002E-2</v>
+        <v>3.3878269999999999E-3</v>
       </c>
       <c r="U56" t="s">
         <v>29</v>
       </c>
       <c r="V56">
-        <v>9.8733296999999998E-2</v>
+        <v>1.7621939999999999E-2</v>
       </c>
       <c r="W56">
         <v>8</v>
@@ -4562,18 +5241,18 @@
         <v>12</v>
       </c>
       <c r="Y56">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="Z56">
-        <v>1762</v>
+        <v>3005</v>
       </c>
     </row>
     <row r="57" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>0.661130886999998</v>
+        <v>0.20747828500000701</v>
       </c>
       <c r="B57">
-        <v>5.0454132606721096</v>
+        <v>26.522252497729301</v>
       </c>
       <c r="C57">
         <v>19.888889312744102</v>
@@ -4591,52 +5270,52 @@
         <v>55</v>
       </c>
       <c r="I57">
-        <v>5849</v>
+        <v>502</v>
       </c>
       <c r="J57">
-        <v>22281</v>
+        <v>32626</v>
       </c>
       <c r="K57">
-        <v>29</v>
+        <v>182</v>
       </c>
       <c r="L57" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M57">
-        <v>2934</v>
+        <v>18512</v>
       </c>
       <c r="N57">
-        <v>5555</v>
+        <v>29201</v>
       </c>
       <c r="O57">
-        <v>2934</v>
+        <v>18512</v>
       </c>
       <c r="P57">
-        <v>5815</v>
+        <v>147</v>
       </c>
       <c r="Q57">
         <v>1</v>
       </c>
       <c r="R57">
-        <v>120130.890721</v>
+        <v>121166.587271</v>
       </c>
       <c r="S57" t="s">
         <v>28</v>
       </c>
       <c r="T57">
-        <v>119.469760534</v>
+        <v>120.959109664</v>
       </c>
       <c r="U57" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V57">
-        <v>120.130890721</v>
+        <v>121.166587271</v>
       </c>
       <c r="W57">
         <v>27</v>
       </c>
       <c r="X57">
-        <v>33</v>
+        <v>353</v>
       </c>
       <c r="Y57">
         <v>0</v>
@@ -4647,10 +5326,10 @@
     </row>
     <row r="58" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A58">
-        <v>0.291755021</v>
+        <v>4.3450514999999898E-2</v>
       </c>
       <c r="B58">
-        <v>4.2481751824817504</v>
+        <v>4.17274939172749</v>
       </c>
       <c r="C58">
         <v>20.049999237060501</v>
@@ -4671,55 +5350,55 @@
         <v>56</v>
       </c>
       <c r="I58">
-        <v>4194</v>
+        <v>200</v>
       </c>
       <c r="J58">
         <v>8176</v>
       </c>
       <c r="K58">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L58" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M58">
-        <v>2012</v>
+        <v>1942</v>
       </c>
       <c r="N58">
-        <v>3492</v>
+        <v>3430</v>
       </c>
       <c r="O58">
-        <v>2012</v>
+        <v>1942</v>
       </c>
       <c r="P58">
-        <v>4104</v>
+        <v>127</v>
       </c>
       <c r="Q58">
         <v>1</v>
       </c>
       <c r="R58">
-        <v>95573.557350999996</v>
+        <v>9517.1194329999998</v>
       </c>
       <c r="S58" t="s">
         <v>28</v>
       </c>
       <c r="T58">
-        <v>93.100395566000003</v>
+        <v>9.4731297530000003</v>
       </c>
       <c r="U58" t="s">
         <v>29</v>
       </c>
       <c r="V58">
-        <v>93.392149855</v>
+        <v>9.5165795190000004</v>
       </c>
       <c r="W58">
         <v>20</v>
       </c>
       <c r="X58">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="Y58">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="Z58">
         <v>8176</v>
@@ -4727,10 +5406,10 @@
     </row>
     <row r="59" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>0.215732281999997</v>
+        <v>3.64466099999999E-2</v>
       </c>
       <c r="B59">
-        <v>2.8062992125984199</v>
+        <v>4.4708661417322801</v>
       </c>
       <c r="C59">
         <v>18.176469802856399</v>
@@ -4742,7 +5421,7 @@
         <v>33</v>
       </c>
       <c r="F59">
-        <v>6568</v>
+        <v>7862</v>
       </c>
       <c r="G59" t="s">
         <v>26</v>
@@ -4751,66 +5430,66 @@
         <v>57</v>
       </c>
       <c r="I59">
-        <v>2539</v>
+        <v>197</v>
       </c>
       <c r="J59">
-        <v>6568</v>
+        <v>8185</v>
       </c>
       <c r="K59">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="L59" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M59">
-        <v>897</v>
+        <v>1710</v>
       </c>
       <c r="N59">
-        <v>1782</v>
+        <v>2839</v>
       </c>
       <c r="O59">
-        <v>897</v>
+        <v>1710</v>
       </c>
       <c r="P59">
-        <v>2476</v>
+        <v>11</v>
       </c>
       <c r="Q59">
         <v>1</v>
       </c>
       <c r="R59">
-        <v>30774.605436000002</v>
+        <v>453.53832299999999</v>
       </c>
       <c r="S59" t="s">
         <v>28</v>
       </c>
       <c r="T59">
-        <v>29.837842800000001</v>
+        <v>0.41671193400000001</v>
       </c>
       <c r="U59" t="s">
         <v>29</v>
       </c>
       <c r="V59">
-        <v>30.053574342000001</v>
+        <v>0.45315786699999999</v>
       </c>
       <c r="W59">
         <v>17</v>
       </c>
       <c r="X59">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="Y59">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="Z59">
-        <v>6568</v>
+        <v>8185</v>
       </c>
     </row>
     <row r="60" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>0.46710453900000398</v>
+        <v>6.7994315000006994E-2</v>
       </c>
       <c r="B60">
-        <v>4.6458504519309702</v>
+        <v>10.8940016433853</v>
       </c>
       <c r="C60">
         <v>20.482759475708001</v>
@@ -4828,52 +5507,52 @@
         <v>58</v>
       </c>
       <c r="I60">
-        <v>4399</v>
+        <v>92</v>
       </c>
       <c r="J60">
-        <v>5075</v>
+        <v>16383</v>
       </c>
       <c r="K60">
-        <v>51</v>
+        <v>97</v>
       </c>
       <c r="L60" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M60">
-        <v>2917</v>
+        <v>7982</v>
       </c>
       <c r="N60">
-        <v>5654</v>
+        <v>13258</v>
       </c>
       <c r="O60">
-        <v>2917</v>
+        <v>7982</v>
       </c>
       <c r="P60">
-        <v>4373</v>
+        <v>24</v>
       </c>
       <c r="Q60">
         <v>1</v>
       </c>
       <c r="R60">
-        <v>120108.625319</v>
+        <v>120271.73508499999</v>
       </c>
       <c r="S60" t="s">
         <v>28</v>
       </c>
       <c r="T60">
-        <v>119.641521736</v>
+        <v>120.203741302</v>
       </c>
       <c r="U60" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V60">
-        <v>120.108625319</v>
+        <v>120.271735085</v>
       </c>
       <c r="W60">
         <v>29</v>
       </c>
       <c r="X60">
-        <v>25</v>
+        <v>67</v>
       </c>
       <c r="Y60">
         <v>0</v>
@@ -4884,10 +5563,10 @@
     </row>
     <row r="61" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A61">
-        <v>0.54981406900000696</v>
+        <v>0.106544443999979</v>
       </c>
       <c r="B61">
-        <v>4.64549839228295</v>
+        <v>9.4734726688102899</v>
       </c>
       <c r="C61">
         <v>21.714284896850501</v>
@@ -4905,52 +5584,52 @@
         <v>59</v>
       </c>
       <c r="I61">
-        <v>4870</v>
+        <v>885</v>
       </c>
       <c r="J61">
-        <v>6775</v>
+        <v>16299</v>
       </c>
       <c r="K61">
-        <v>48</v>
+        <v>87</v>
       </c>
       <c r="L61" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M61">
-        <v>2898</v>
+        <v>6763</v>
       </c>
       <c r="N61">
-        <v>5779</v>
+        <v>11785</v>
       </c>
       <c r="O61">
-        <v>2898</v>
+        <v>6763</v>
       </c>
       <c r="P61">
-        <v>4845</v>
+        <v>828</v>
       </c>
       <c r="Q61">
         <v>1</v>
       </c>
       <c r="R61">
-        <v>120139.762651</v>
+        <v>136833.378749</v>
       </c>
       <c r="S61" t="s">
         <v>28</v>
       </c>
       <c r="T61">
-        <v>119.58994934099999</v>
+        <v>136.72683493700001</v>
       </c>
       <c r="U61" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="V61">
-        <v>120.139762651</v>
+        <v>136.83337874899999</v>
       </c>
       <c r="W61">
         <v>28</v>
       </c>
       <c r="X61">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="Y61">
         <v>0</v>
@@ -4961,10 +5640,10 @@
     </row>
     <row r="62" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A62">
-        <v>0.36094625899999799</v>
+        <v>2.89215299999999E-2</v>
       </c>
       <c r="B62">
-        <v>3.14797507788162</v>
+        <v>2.8676012461059099</v>
       </c>
       <c r="C62">
         <v>17.3333339691162</v>
@@ -4985,7 +5664,7 @@
         <v>60</v>
       </c>
       <c r="I62">
-        <v>4270</v>
+        <v>437</v>
       </c>
       <c r="J62">
         <v>5016</v>
@@ -4994,46 +5673,46 @@
         <v>11</v>
       </c>
       <c r="L62" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M62">
-        <v>1048</v>
+        <v>948</v>
       </c>
       <c r="N62">
-        <v>2021</v>
+        <v>1841</v>
       </c>
       <c r="O62">
-        <v>1048</v>
+        <v>948</v>
       </c>
       <c r="P62">
-        <v>4195</v>
+        <v>391</v>
       </c>
       <c r="Q62">
         <v>1</v>
       </c>
       <c r="R62">
-        <v>24274.269956</v>
+        <v>267.78795000000002</v>
       </c>
       <c r="S62" t="s">
         <v>28</v>
       </c>
       <c r="T62">
-        <v>23.158294065</v>
+        <v>0.23842872300000001</v>
       </c>
       <c r="U62" t="s">
         <v>29</v>
       </c>
       <c r="V62">
-        <v>23.519239682999999</v>
+        <v>0.26734974</v>
       </c>
       <c r="W62">
         <v>18</v>
       </c>
       <c r="X62">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="Y62">
-        <v>29</v>
+        <v>11</v>
       </c>
       <c r="Z62">
         <v>5016</v>
@@ -5041,10 +5720,10 @@
     </row>
     <row r="63" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A63">
-        <v>2.0210189999999999E-2</v>
+        <v>1.3270311E-2</v>
       </c>
       <c r="B63">
-        <v>1.84313725490196</v>
+        <v>1.91503267973856</v>
       </c>
       <c r="C63">
         <v>14.800000190734799</v>
@@ -5065,66 +5744,66 @@
         <v>61</v>
       </c>
       <c r="I63">
-        <v>454</v>
+        <v>52</v>
       </c>
       <c r="J63">
-        <v>4798</v>
+        <v>4818</v>
       </c>
       <c r="K63">
         <v>4</v>
       </c>
       <c r="L63" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M63">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N63">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="O63">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="P63">
-        <v>419</v>
+        <v>21</v>
       </c>
       <c r="Q63">
         <v>1</v>
       </c>
       <c r="R63">
-        <v>39.259942000000002</v>
+        <v>14.285629999999999</v>
       </c>
       <c r="S63" t="s">
         <v>28</v>
       </c>
       <c r="T63">
-        <v>1.8905622E-2</v>
+        <v>9.8298000000000005E-4</v>
       </c>
       <c r="U63" t="s">
         <v>29</v>
       </c>
       <c r="V63">
-        <v>3.9115245E-2</v>
+        <v>1.4252872E-2</v>
       </c>
       <c r="W63">
         <v>5</v>
       </c>
       <c r="X63">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y63">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="Z63">
-        <v>4798</v>
+        <v>4818</v>
       </c>
     </row>
     <row r="64" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A64">
-        <v>1.6835155000000001E-2</v>
+        <v>1.3959459E-2</v>
       </c>
       <c r="B64">
-        <v>3.56069364161849</v>
+        <v>3.4797687861271598</v>
       </c>
       <c r="C64">
         <v>16.799999237060501</v>
@@ -5136,7 +5815,7 @@
         <v>20</v>
       </c>
       <c r="F64">
-        <v>674</v>
+        <v>862</v>
       </c>
       <c r="G64" t="s">
         <v>26</v>
@@ -5145,66 +5824,66 @@
         <v>62</v>
       </c>
       <c r="I64">
-        <v>232</v>
+        <v>82</v>
       </c>
       <c r="J64">
-        <v>674</v>
+        <v>863</v>
       </c>
       <c r="K64">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M64">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="N64">
-        <v>616</v>
+        <v>602</v>
       </c>
       <c r="O64">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="P64">
-        <v>173</v>
+        <v>24</v>
       </c>
       <c r="Q64">
         <v>1</v>
       </c>
       <c r="R64">
-        <v>32.029431000000002</v>
+        <v>15.902138000000001</v>
       </c>
       <c r="S64" t="s">
         <v>28</v>
       </c>
       <c r="T64">
-        <v>1.5077597999999999E-2</v>
+        <v>1.8894129999999999E-3</v>
       </c>
       <c r="U64" t="s">
         <v>29</v>
       </c>
       <c r="V64">
-        <v>3.1912184000000003E-2</v>
+        <v>1.5848251000000001E-2</v>
       </c>
       <c r="W64">
         <v>5</v>
       </c>
       <c r="X64">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Y64">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Z64">
-        <v>674</v>
+        <v>863</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65">
-        <v>0.38801246899998798</v>
+        <v>3.8407515999999899E-2</v>
       </c>
       <c r="B65">
-        <v>4.0258358662613896</v>
+        <v>6.1656534954407203</v>
       </c>
       <c r="C65">
         <v>15.949999809265099</v>
@@ -5216,7 +5895,7 @@
         <v>25</v>
       </c>
       <c r="F65">
-        <v>62703</v>
+        <v>63261</v>
       </c>
       <c r="G65" t="s">
         <v>26</v>
@@ -5225,66 +5904,66 @@
         <v>63</v>
       </c>
       <c r="I65">
-        <v>4227</v>
+        <v>177</v>
       </c>
       <c r="J65">
-        <v>62703</v>
+        <v>65525</v>
       </c>
       <c r="K65">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="L65" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M65">
-        <v>1477</v>
+        <v>2504</v>
       </c>
       <c r="N65">
-        <v>2649</v>
+        <v>4057</v>
       </c>
       <c r="O65">
-        <v>1477</v>
+        <v>2504</v>
       </c>
       <c r="P65">
-        <v>4181</v>
+        <v>14</v>
       </c>
       <c r="Q65">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="R65">
-        <v>83710.721925000005</v>
+        <v>426.04757499999999</v>
       </c>
       <c r="S65" t="s">
         <v>28</v>
       </c>
       <c r="T65">
-        <v>81.079279232000005</v>
+        <v>0.387148194</v>
       </c>
       <c r="U65" t="s">
         <v>29</v>
       </c>
       <c r="V65">
-        <v>81.467291005999996</v>
+        <v>0.42555504599999999</v>
       </c>
       <c r="W65">
         <v>20</v>
       </c>
       <c r="X65">
-        <v>44</v>
+        <v>129</v>
       </c>
       <c r="Y65">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Z65">
-        <v>62703</v>
+        <v>65525</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66">
-        <v>2.8810637E-2</v>
+        <v>2.3749992000000001E-2</v>
       </c>
       <c r="B66">
-        <v>4.4316939890710296</v>
+        <v>4.70491803278688</v>
       </c>
       <c r="C66">
         <v>17.799999237060501</v>
@@ -5305,55 +5984,55 @@
         <v>64</v>
       </c>
       <c r="I66">
-        <v>671</v>
+        <v>378</v>
       </c>
       <c r="J66">
         <v>1485</v>
       </c>
       <c r="K66">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="L66" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M66">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="N66">
-        <v>811</v>
+        <v>861</v>
       </c>
       <c r="O66">
-        <v>474</v>
+        <v>500</v>
       </c>
       <c r="P66">
-        <v>585</v>
+        <v>312</v>
       </c>
       <c r="Q66">
         <v>1</v>
       </c>
       <c r="R66">
-        <v>150.749515</v>
+        <v>62.304271999999997</v>
       </c>
       <c r="S66" t="s">
         <v>28</v>
       </c>
       <c r="T66">
-        <v>0.121648864</v>
+        <v>3.8186050999999999E-2</v>
       </c>
       <c r="U66" t="s">
         <v>29</v>
       </c>
       <c r="V66">
-        <v>0.15045877299999999</v>
+        <v>6.1935587E-2</v>
       </c>
       <c r="W66">
         <v>5</v>
       </c>
       <c r="X66">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="Y66">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="Z66">
         <v>1485</v>
@@ -5361,10 +6040,10 @@
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67">
-        <v>1.3358607999999999E-2</v>
+        <v>1.3602852E-2</v>
       </c>
       <c r="B67">
-        <v>1.85987261146496</v>
+        <v>2.0127388535031798</v>
       </c>
       <c r="C67">
         <v>15.199999809265099</v>
@@ -5385,66 +6064,66 @@
         <v>65</v>
       </c>
       <c r="I67">
-        <v>112</v>
+        <v>62</v>
       </c>
       <c r="J67">
-        <v>461</v>
+        <v>503</v>
       </c>
       <c r="K67">
         <v>4</v>
       </c>
       <c r="L67" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M67">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="N67">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="O67">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="P67">
-        <v>66</v>
+        <v>12</v>
       </c>
       <c r="Q67">
         <v>1</v>
       </c>
       <c r="R67">
-        <v>14.480352</v>
+        <v>14.075944</v>
       </c>
       <c r="S67" t="s">
         <v>28</v>
       </c>
       <c r="T67">
-        <v>1.092733E-3</v>
+        <v>4.34074E-4</v>
       </c>
       <c r="U67" t="s">
         <v>29</v>
       </c>
       <c r="V67">
-        <v>1.4450866999999999E-2</v>
+        <v>1.4036297E-2</v>
       </c>
       <c r="W67">
         <v>5</v>
       </c>
       <c r="X67">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Y67">
         <v>43</v>
       </c>
       <c r="Z67">
-        <v>461</v>
+        <v>503</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A68">
-        <v>0.45281953099998801</v>
+        <v>5.0697268999999601E-2</v>
       </c>
       <c r="B68">
-        <v>3.1164021164021101</v>
+        <v>6.0092592592592498</v>
       </c>
       <c r="C68">
         <v>15.25</v>
@@ -5455,6 +6134,9 @@
       <c r="E68">
         <v>25</v>
       </c>
+      <c r="F68">
+        <v>61182</v>
+      </c>
       <c r="G68" t="s">
         <v>26</v>
       </c>
@@ -5462,61 +6144,67 @@
         <v>66</v>
       </c>
       <c r="I68">
-        <v>4927</v>
+        <v>182</v>
       </c>
       <c r="J68">
-        <v>58170</v>
+        <v>62626</v>
       </c>
       <c r="K68">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="L68" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M68">
-        <v>1178</v>
+        <v>2792</v>
       </c>
       <c r="N68">
-        <v>2356</v>
+        <v>4543</v>
       </c>
       <c r="O68">
-        <v>1178</v>
+        <v>2792</v>
       </c>
       <c r="P68">
-        <v>4895</v>
+        <v>8</v>
       </c>
       <c r="Q68">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R68">
-        <v>120035.470455</v>
+        <v>2529.039475</v>
       </c>
       <c r="S68" t="s">
         <v>28</v>
       </c>
       <c r="T68">
-        <v>119.58265164700001</v>
+        <v>2.4772854940000002</v>
       </c>
       <c r="U68" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="V68">
-        <v>120.035470455</v>
+        <v>2.5279821920000001</v>
       </c>
       <c r="W68">
         <v>24</v>
       </c>
       <c r="X68">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="Y68">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="Z68">
-        <v>59479</v>
+        <v>62626</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>1.4421508E-2</v>
+      </c>
+      <c r="B69">
+        <v>3.2086330935251799</v>
+      </c>
       <c r="C69">
         <v>13.399999618530201</v>
       </c>
@@ -5526,29 +6214,77 @@
       <c r="E69">
         <v>25</v>
       </c>
+      <c r="F69">
+        <v>2622</v>
+      </c>
       <c r="G69" t="s">
         <v>26</v>
       </c>
       <c r="H69">
         <v>67</v>
       </c>
+      <c r="I69">
+        <v>86</v>
+      </c>
+      <c r="J69">
+        <v>2747</v>
+      </c>
+      <c r="K69">
+        <v>7</v>
+      </c>
       <c r="L69" t="s">
-        <v>98</v>
+        <v>97</v>
+      </c>
+      <c r="M69">
+        <v>253</v>
+      </c>
+      <c r="N69">
+        <v>446</v>
+      </c>
+      <c r="O69">
+        <v>253</v>
+      </c>
+      <c r="P69">
+        <v>14</v>
+      </c>
+      <c r="Q69">
+        <v>2</v>
       </c>
       <c r="R69">
-        <v>120000</v>
+        <v>16.076488000000001</v>
       </c>
       <c r="S69" t="s">
         <v>28</v>
       </c>
+      <c r="T69">
+        <v>1.531389E-3</v>
+      </c>
       <c r="U69" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V69">
+        <v>1.5952362000000001E-2</v>
       </c>
       <c r="W69">
         <v>5</v>
       </c>
+      <c r="X69">
+        <v>11</v>
+      </c>
+      <c r="Y69">
+        <v>58</v>
+      </c>
+      <c r="Z69">
+        <v>2747</v>
+      </c>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>1.5504001E-2</v>
+      </c>
+      <c r="B70">
+        <v>2.9695431472081202</v>
+      </c>
       <c r="C70">
         <v>13.571428298950099</v>
       </c>
@@ -5558,34 +6294,76 @@
       <c r="E70">
         <v>25</v>
       </c>
+      <c r="F70">
+        <v>12790</v>
+      </c>
       <c r="G70" t="s">
         <v>26</v>
       </c>
       <c r="H70">
         <v>68</v>
       </c>
+      <c r="I70">
+        <v>137</v>
+      </c>
+      <c r="J70">
+        <v>12793</v>
+      </c>
+      <c r="K70">
+        <v>10</v>
+      </c>
       <c r="L70" t="s">
-        <v>99</v>
+        <v>98</v>
+      </c>
+      <c r="M70">
+        <v>260</v>
+      </c>
+      <c r="N70">
+        <v>585</v>
+      </c>
+      <c r="O70">
+        <v>260</v>
+      </c>
+      <c r="P70">
+        <v>87</v>
+      </c>
+      <c r="Q70">
+        <v>1</v>
       </c>
       <c r="R70">
-        <v>120000</v>
+        <v>22.050878999999998</v>
       </c>
       <c r="S70" t="s">
         <v>28</v>
       </c>
+      <c r="T70">
+        <v>6.4333189999999998E-3</v>
+      </c>
       <c r="U70" t="s">
-        <v>32</v>
+        <v>29</v>
+      </c>
+      <c r="V70">
+        <v>2.1936656999999998E-2</v>
       </c>
       <c r="W70">
         <v>7</v>
       </c>
+      <c r="X70">
+        <v>21</v>
+      </c>
+      <c r="Y70">
+        <v>27</v>
+      </c>
+      <c r="Z70">
+        <v>12793</v>
+      </c>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A71">
-        <v>1.4130037E-2</v>
+        <v>1.2717688E-2</v>
       </c>
       <c r="B71">
-        <v>1.5026737967914401</v>
+        <v>1.49197860962566</v>
       </c>
       <c r="C71">
         <v>12.857142448425201</v>
@@ -5597,7 +6375,7 @@
         <v>25</v>
       </c>
       <c r="F71">
-        <v>8761</v>
+        <v>11743</v>
       </c>
       <c r="G71" t="s">
         <v>26</v>
@@ -5606,66 +6384,66 @@
         <v>69</v>
       </c>
       <c r="I71">
-        <v>107</v>
+        <v>46</v>
       </c>
       <c r="J71">
-        <v>8761</v>
+        <v>16208</v>
       </c>
       <c r="K71">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L71" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M71">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="N71">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="O71">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="P71">
-        <v>71</v>
+        <v>8</v>
       </c>
       <c r="Q71">
         <v>1</v>
       </c>
       <c r="R71">
-        <v>16.153901999999999</v>
+        <v>13.234595000000001</v>
       </c>
       <c r="S71" t="s">
         <v>28</v>
       </c>
       <c r="T71">
-        <v>1.980075E-3</v>
+        <v>4.7697800000000003E-4</v>
       </c>
       <c r="U71" t="s">
         <v>29</v>
       </c>
       <c r="V71">
-        <v>1.6109500999999998E-2</v>
+        <v>1.3193946999999999E-2</v>
       </c>
       <c r="W71">
         <v>7</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y71">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="Z71">
-        <v>8761</v>
+        <v>16208</v>
       </c>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A72">
-        <v>0.78844638600000305</v>
+        <v>0.157662948999999</v>
       </c>
       <c r="B72">
-        <v>3.0452830188679201</v>
+        <v>3.37232704402515</v>
       </c>
       <c r="C72">
         <v>15.399999618530201</v>
@@ -5676,6 +6454,9 @@
       <c r="E72">
         <v>25</v>
       </c>
+      <c r="F72">
+        <v>80967</v>
+      </c>
       <c r="G72" t="s">
         <v>26</v>
       </c>
@@ -5683,66 +6464,66 @@
         <v>70</v>
       </c>
       <c r="I72">
-        <v>7495</v>
+        <v>3724</v>
       </c>
       <c r="J72">
-        <v>72059</v>
+        <v>126834</v>
       </c>
       <c r="K72">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="L72" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="M72">
-        <v>1185</v>
+        <v>1453</v>
       </c>
       <c r="N72">
-        <v>2421</v>
+        <v>2681</v>
       </c>
       <c r="O72">
-        <v>1185</v>
+        <v>1453</v>
       </c>
       <c r="P72">
-        <v>7459</v>
+        <v>3641</v>
       </c>
       <c r="Q72">
         <v>1</v>
       </c>
       <c r="R72">
-        <v>120133.924359</v>
+        <v>1687.395608</v>
       </c>
       <c r="S72" t="s">
         <v>28</v>
       </c>
       <c r="T72">
-        <v>119.345478683</v>
+        <v>1.5282026040000001</v>
       </c>
       <c r="U72" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="V72">
-        <v>120.13392435900001</v>
+        <v>1.685864976</v>
       </c>
       <c r="W72">
         <v>25</v>
       </c>
       <c r="X72">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="Y72">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="Z72">
-        <v>73988</v>
+        <v>126834</v>
       </c>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A73">
-        <v>1.5674793539999901</v>
+        <v>0.43637171600000002</v>
       </c>
       <c r="B73">
-        <v>3.4658119658119602</v>
+        <v>5.4444444444444402</v>
       </c>
       <c r="C73">
         <v>16.214284896850501</v>
@@ -5753,6 +6534,9 @@
       <c r="E73">
         <v>25</v>
       </c>
+      <c r="F73">
+        <v>25346</v>
+      </c>
       <c r="G73" t="s">
         <v>26</v>
       </c>
@@ -5760,58 +6544,58 @@
         <v>71</v>
       </c>
       <c r="I73">
-        <v>12902</v>
+        <v>6092</v>
       </c>
       <c r="J73">
-        <v>16751</v>
+        <v>25502</v>
       </c>
       <c r="K73">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="L73" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="M73">
-        <v>699</v>
+        <v>1337</v>
       </c>
       <c r="N73">
-        <v>1622</v>
+        <v>2548</v>
       </c>
       <c r="O73">
-        <v>699</v>
+        <v>1337</v>
       </c>
       <c r="P73">
-        <v>12867</v>
+        <v>5952</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R73">
-        <v>120008.068314</v>
+        <v>14641.458513</v>
       </c>
       <c r="S73" t="s">
         <v>28</v>
       </c>
       <c r="T73">
-        <v>118.440589735</v>
+        <v>15.848111316000001</v>
       </c>
       <c r="U73" t="s">
-        <v>53</v>
+        <v>29</v>
       </c>
       <c r="V73">
-        <v>120.008068314</v>
+        <v>16.284482382</v>
       </c>
       <c r="W73">
         <v>14</v>
       </c>
       <c r="X73">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="Y73">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="Z73">
-        <v>21582</v>
+        <v>25502</v>
       </c>
     </row>
   </sheetData>
